--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -102,14 +102,14 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="001F2430"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="002E5C8A"/>
       <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001F2430"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -321,7 +321,16 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -336,22 +345,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -1792,26 +1792,32 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C3" s="29" t="n"/>
+      <c r="C3" s="29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" s="30" t="inlineStr">
         <is>
-          <t>רותם דרור, ארבל פרנקו, יונתן לירז</t>
-        </is>
-      </c>
-      <c r="H3" s="19" t="n"/>
+          <t>רגב שהם, איתן כהן, ירדן בן שחר, טליה קור, יהב לוי</t>
+        </is>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>חלות</t>
+        </is>
+      </c>
       <c r="I3" s="27" t="n">
         <v>1</v>
       </c>
@@ -1833,26 +1839,32 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n"/>
+      <c r="C4" s="29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בצק, מילוי, קליעת קראנץ' ואפייה</t>
         </is>
       </c>
       <c r="F4" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="30" t="inlineStr">
         <is>
-          <t>יותם ספיר, ירדן בן שחר, טליה קור</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="n"/>
+          <t>עשהאל ירושלמי, הדר עמדי, מישל דוד, משה אוברשטיין</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>עוגות שמרים (קראנץ' קינמון ושוקולד)</t>
+        </is>
+      </c>
       <c r="I4" s="27" t="n">
         <v>1</v>
       </c>
@@ -1874,26 +1886,32 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n"/>
+      <c r="C5" s="29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בישול ארוך עד מרקם ריבתי</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" s="30" t="inlineStr">
         <is>
-          <t>סהר שירון, שחר מרקוביץ' גליק, רוני כהן</t>
-        </is>
-      </c>
-      <c r="H5" s="19" t="n"/>
+          <t>שירה אדלה לוזון, זואי כהן, אלה גוטליב, יונתן לירז</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>מטבוחה</t>
+        </is>
+      </c>
       <c r="I5" s="27" t="n">
         <v>1</v>
       </c>
@@ -1915,15 +1933,17 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
+      <c r="C6" s="29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>עוגות · צוות שילת</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>אפיית 10–12 תבניות אינגליש</t>
         </is>
       </c>
       <c r="F6" s="27" t="n">
@@ -1931,10 +1951,14 @@
       </c>
       <c r="G6" s="30" t="inlineStr">
         <is>
-          <t>שילת פילפל, שירה ספונוב</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="n"/>
+          <t>איתי בן מנחם, פרת פולס</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>עוגת דבש</t>
+        </is>
+      </c>
       <c r="I6" s="27" t="n">
         <v>1</v>
       </c>
@@ -1957,33 +1981,37 @@
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
+          <t>הכנת הבצק, כדרור ואפייה</t>
         </is>
       </c>
       <c r="F7" s="27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" s="30" t="inlineStr">
         <is>
-          <t>ינון לוי, שי- לי וולגמוט, עשהאל ירושלמי, של״ו רובינשטיין</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="n"/>
+          <t>שחר מרקוביץ' גליק, עמרי קולטון</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>עוגיות שוקולד צ'יפס</t>
+        </is>
+      </c>
       <c r="I7" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K7" s="20" t="n"/>
@@ -2000,33 +2028,37 @@
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>המסה, ערבוב ואפייה</t>
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="30" t="inlineStr">
         <is>
-          <t>ינון לוי, שי- לי וולגמוט, עשהאל ירושלמי, של״ו רובינשטיין</t>
-        </is>
-      </c>
-      <c r="H8" s="19" t="n"/>
+          <t>איתן וינסטון, יעל שם טוב</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>בראוניז ללא גלוטן</t>
+        </is>
+      </c>
       <c r="I8" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K8" s="20" t="n"/>
@@ -2034,7 +2066,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="B9" s="28" t="inlineStr">
@@ -2043,16 +2075,16 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>סלט חצילים</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>קלייה, סינון, קיצוץ ותיבול</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
@@ -2060,16 +2092,20 @@
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>יהונתן קצב, פרת פולס</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="n"/>
+          <t>חיים שמאי, אלרואי גרינברג</t>
+        </is>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>סלט חצילים קלויים</t>
+        </is>
+      </c>
       <c r="I9" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K9" s="20" t="n"/>
@@ -2077,7 +2113,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="B10" s="28" t="inlineStr">
@@ -2086,16 +2122,16 @@
         </is>
       </c>
       <c r="C10" s="29" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>הכנת החומוס</t>
         </is>
       </c>
       <c r="F10" s="27" t="n">
@@ -2103,7 +2139,7 @@
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
-          <t>יהב לוי, עמית שי אברהם</t>
+          <t>ליבי בוכריס, רוני כהן</t>
         </is>
       </c>
       <c r="H10" s="19" t="n"/>
@@ -2112,7 +2148,7 @@
       </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K10" s="20" t="n"/>
@@ -2120,7 +2156,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="B11" s="28" t="inlineStr">
@@ -2129,24 +2165,24 @@
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>0.8125</v>
+        <v>0.5</v>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>הגשת ארוחת הצהריים</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="30" t="inlineStr">
         <is>
-          <t>איתי בן מנחם, איתן כהן, יהונתן קצב</t>
+          <t>ליבי בוכריס, רוני כהן</t>
         </is>
       </c>
       <c r="H11" s="19" t="n"/>
@@ -2155,7 +2191,7 @@
       </c>
       <c r="J11" s="19" t="inlineStr">
         <is>
-          <t>קבלת שבת וערבית</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="K11" s="20" t="n"/>
@@ -2163,7 +2199,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="B12" s="28" t="inlineStr">
@@ -2172,24 +2208,24 @@
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>0.8125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>קיפול הארוחה, שטיפת כלים</t>
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
-          <t>פרת פולס, יהב לוי, עמית שי אברהם</t>
+          <t>ליבי בוכריס, רוני כהן</t>
         </is>
       </c>
       <c r="H12" s="19" t="n"/>
@@ -2198,7 +2234,7 @@
       </c>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>קבלת שבת וערבית</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="K12" s="20" t="n"/>
@@ -2206,7 +2242,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B13" s="28" t="inlineStr">
@@ -2215,24 +2251,24 @@
         </is>
       </c>
       <c r="C13" s="29" t="n">
-        <v>0.875</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="30" t="inlineStr">
         <is>
-          <t>איתי בן מנחם, איתן כהן</t>
+          <t>אנה עזריאל, של״ו רובינשטיין, ארבל פרנקו, עופר בביוף, אורי אסף, עמית שי אברהם</t>
         </is>
       </c>
       <c r="H13" s="19" t="n"/>
@@ -2241,7 +2277,7 @@
       </c>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K13" s="20" t="n"/>
@@ -2249,7 +2285,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B14" s="28" t="inlineStr">
@@ -2258,24 +2294,24 @@
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>0.875</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>חיתוך אבטיח</t>
+          <t>טאטוא ושטיפת רצפה</t>
         </is>
       </c>
       <c r="F14" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="30" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>הילי אלפסי, שליו שישו, תמר פרידמן</t>
         </is>
       </c>
       <c r="H14" s="19" t="n"/>
@@ -2284,7 +2320,7 @@
       </c>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K14" s="20" t="n"/>
@@ -2292,7 +2328,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B15" s="28" t="inlineStr">
@@ -2301,24 +2337,24 @@
         </is>
       </c>
       <c r="C15" s="29" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>תליית מחיצה</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="30" t="inlineStr">
         <is>
-          <t>פרת פולס, יהב לוי, עמית שי אברהם</t>
+          <t>יהונתן קצב, איתי רוס</t>
         </is>
       </c>
       <c r="H15" s="19" t="n"/>
@@ -2327,7 +2363,7 @@
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K15" s="20" t="n"/>
@@ -2335,7 +2371,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B16" s="28" t="inlineStr">
@@ -2344,24 +2380,24 @@
         </is>
       </c>
       <c r="C16" s="29" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D16" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
         </is>
       </c>
       <c r="F16" s="27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="30" t="inlineStr">
         <is>
-          <t>איתי בן מנחם, איתן כהן, יהונתן קצב</t>
+          <t>עומר יוסף גנון, אלה מאיר, פנחס אליהו גלוסקין, שירה ספונוב</t>
         </is>
       </c>
       <c r="H16" s="19" t="n"/>
@@ -2370,7 +2406,7 @@
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K16" s="20" t="n"/>
@@ -2378,7 +2414,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B17" s="28" t="inlineStr">
@@ -2386,21 +2422,25 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n"/>
+      <c r="C17" s="29" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
-        </is>
-      </c>
-      <c r="F17" s="27" t="n"/>
+          <t>הנחת סידורים על הכסאות</t>
+        </is>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="G17" s="30" t="inlineStr">
         <is>
-          <t>יהונתן קצב, פרת פולס, יהב לוי, עמית שי אברהם, איתי בן מנחם, איתן כהן</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="H17" s="19" t="n"/>
@@ -2409,7 +2449,7 @@
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K17" s="20" t="n"/>
@@ -2417,33 +2457,33 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+          <t>עזרה בהכנת החלות</t>
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>שליו שישו</t>
+          <t>אנה עזריאל, של״ו רובינשטיין, ארבל פרנקו, עופר בביוף, אורי אסף, עמית שי אברהם, הילי אלפסי, שליו שישו</t>
         </is>
       </c>
       <c r="H18" s="19" t="n"/>
@@ -2452,7 +2492,7 @@
       </c>
       <c r="J18" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K18" s="20" t="n"/>
@@ -2460,33 +2500,33 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B19" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>חימום עוגות</t>
+          <t>עזרה בהכנת עוגות השמרים</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G19" s="30" t="inlineStr">
         <is>
-          <t>פנחס אליהו גלוסקין</t>
+          <t>תמר פרידמן, יהונתן קצב, איתי רוס, עומר יוסף גנון, אלה מאיר, פנחס אליהו גלוסקין, שירה ספונוב, נגה חוה כהן</t>
         </is>
       </c>
       <c r="H19" s="19" t="n"/>
@@ -2495,7 +2535,7 @@
       </c>
       <c r="J19" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="K19" s="20" t="n"/>
@@ -2506,30 +2546,30 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>אביב רוזנטל</t>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים</t>
         </is>
       </c>
       <c r="H20" s="19" t="n"/>
@@ -2538,7 +2578,7 @@
       </c>
       <c r="J20" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="K20" s="20" t="n"/>
@@ -2549,39 +2589,43 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="n"/>
+          <t>הלל פינגולד, יובל יצחק</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן</t>
+        </is>
+      </c>
       <c r="I21" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="K21" s="20" t="n"/>
@@ -2592,22 +2636,22 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C22" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>חיתוך האבטיח</t>
+          <t>הכנת סלט טחינה — חצי כמות לארוחת הערב</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
@@ -2615,16 +2659,20 @@
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>יעל שם טוב</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="n"/>
+          <t>אביב רוזנטל</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
+        <is>
+          <t>סלט טחינה ביתית</t>
+        </is>
+      </c>
       <c r="I22" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="K22" s="20" t="n"/>
@@ -2635,30 +2683,30 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C23" s="29" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>הנחת האוכל בתנור החימום</t>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>איתי בן מנחם, נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="H23" s="19" t="n"/>
@@ -2667,7 +2715,7 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="K23" s="20" t="n"/>
@@ -2678,30 +2726,30 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C24" s="29" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
         </is>
       </c>
       <c r="F24" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>עמרי קולטון, יובל יצחק</t>
+          <t>איתמר אסנהיים, הלל פינגולד, יובל יצחק</t>
         </is>
       </c>
       <c r="H24" s="19" t="n"/>
@@ -2710,7 +2758,7 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>חבורות</t>
+          <t>קבלת שבת וערבית</t>
         </is>
       </c>
       <c r="K24" s="20" t="n"/>
@@ -2721,22 +2769,22 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C25" s="29" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
@@ -2744,7 +2792,7 @@
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
-          <t>אורי אסף, זואי כהן, איתי רוס</t>
+          <t>אביב רוזנטל, איתי בן מנחם, נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="H25" s="19" t="n"/>
@@ -2753,7 +2801,7 @@
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>חבורות</t>
+          <t>קבלת שבת וערבית</t>
         </is>
       </c>
       <c r="K25" s="20" t="n"/>
@@ -2764,224 +2812,678 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="19" t="n"/>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C26" s="29" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>כולם בבית המדרש לחלוקת גזרות</t>
-        </is>
-      </c>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="30" t="n"/>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="30" t="inlineStr">
+        <is>
+          <t>איתמר אסנהיים, הלל פינגולד</t>
+        </is>
+      </c>
       <c r="H26" s="19" t="n"/>
       <c r="I26" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>ניקיונות מוצ"ש</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="K26" s="20" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="27" t="n"/>
-      <c r="B27" s="27" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="30" t="n"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>חיתוך אבטיח</t>
+        </is>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="30" t="inlineStr">
+        <is>
+          <t>יובל יצחק</t>
+        </is>
+      </c>
       <c r="H27" s="19" t="n"/>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="19" t="n"/>
+      <c r="I27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
       <c r="K27" s="20" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="27" t="n"/>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="30" t="n"/>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>אביב רוזנטל, איתי בן מנחם, נועם ישראל קומפאס</t>
+        </is>
+      </c>
       <c r="H28" s="19" t="n"/>
-      <c r="I28" s="27" t="n"/>
-      <c r="J28" s="19" t="n"/>
+      <c r="I28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
       <c r="K28" s="20" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="27" t="n"/>
-      <c r="B29" s="27" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="30" t="n"/>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="30" t="inlineStr">
+        <is>
+          <t>איתמר אסנהיים, הלל פינגולד, יובל יצחק</t>
+        </is>
+      </c>
       <c r="H29" s="19" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="19" t="n"/>
+      <c r="I29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>סעודת שבת</t>
+        </is>
+      </c>
       <c r="K29" s="20" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="27" t="n"/>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
       <c r="C30" s="29" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="20" t="n"/>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+        </is>
+      </c>
       <c r="F30" s="27" t="n"/>
-      <c r="G30" s="30" t="n"/>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
+        </is>
+      </c>
       <c r="H30" s="19" t="n"/>
-      <c r="I30" s="27" t="n"/>
-      <c r="J30" s="19" t="n"/>
+      <c r="I30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>טיש בחדר אוכל</t>
+        </is>
+      </c>
       <c r="K30" s="20" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="27" t="n"/>
-      <c r="B31" s="27" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="30" t="n"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="30" t="inlineStr">
+        <is>
+          <t>רותם דרור</t>
+        </is>
+      </c>
       <c r="H31" s="19" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="19" t="n"/>
+      <c r="I31" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K31" s="20" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="27" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="30" t="n"/>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>חימום עוגות</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>אחיה נחמני</t>
+        </is>
+      </c>
       <c r="H32" s="19" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="19" t="n"/>
+      <c r="I32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K32" s="20" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="27" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="30" t="n"/>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C33" s="29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="30" t="inlineStr">
+        <is>
+          <t>מישל דוד</t>
+        </is>
+      </c>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="19" t="n"/>
+      <c r="I33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K33" s="20" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="30" t="n"/>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>זואי כהן</t>
+        </is>
+      </c>
       <c r="H34" s="19" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="19" t="n"/>
+      <c r="I34" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K34" s="20" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="30" t="n"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>חיתוך האבטיח</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="30" t="inlineStr">
+        <is>
+          <t>נגה שוהם</t>
+        </is>
+      </c>
       <c r="H35" s="19" t="n"/>
-      <c r="I35" s="27" t="n"/>
-      <c r="J35" s="19" t="n"/>
+      <c r="I35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K35" s="20" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="29" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="20" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="30" t="n"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr">
+        <is>
+          <t>הנחת האוכל בתנור החימום</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>שירה אדלה לוזון</t>
+        </is>
+      </c>
       <c r="H36" s="19" t="n"/>
-      <c r="I36" s="27" t="n"/>
-      <c r="J36" s="19" t="n"/>
+      <c r="I36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K36" s="20" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="27" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="19" t="n"/>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C37" s="29" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+        </is>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="30" t="inlineStr">
+        <is>
+          <t>טליה קור, רוני פרנקל</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן</t>
+        </is>
+      </c>
+      <c r="I37" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K37" s="20" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="19" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="19" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="19" t="n"/>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t>הכנת סלט טחינה — חצי כמות לארוחת הצהריים</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>אלה גוטליב</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="inlineStr">
+        <is>
+          <t>סלט טחינה ביתית</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="K38" s="20" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="27" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="30" t="n"/>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="30" t="inlineStr">
+        <is>
+          <t>הדר עמדי, שירה אדלה לוזון</t>
+        </is>
+      </c>
       <c r="H39" s="19" t="n"/>
-      <c r="I39" s="27" t="n"/>
-      <c r="J39" s="19" t="n"/>
+      <c r="I39" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>חבורות</t>
+        </is>
+      </c>
       <c r="K39" s="20" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="27" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="29" t="n"/>
-      <c r="D40" s="19" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="30" t="n"/>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>טליה קור, רוני פרנקל, אלה גוטליב</t>
+        </is>
+      </c>
       <c r="H40" s="19" t="n"/>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="19" t="n"/>
+      <c r="I40" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>חבורות</t>
+        </is>
+      </c>
       <c r="K40" s="20" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="27" t="n"/>
-      <c r="B41" s="27" t="n"/>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
       <c r="C41" s="29" t="n"/>
       <c r="D41" s="19" t="n"/>
-      <c r="E41" s="20" t="n"/>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>כולם בבית המדרש לחלוקת גזרות</t>
+        </is>
+      </c>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="30" t="n"/>
       <c r="H41" s="19" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="19" t="n"/>
+      <c r="I41" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>ניקיונות מוצ"ש</t>
+        </is>
+      </c>
       <c r="K41" s="20" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -4135,7 +4637,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="B3" s="27" t="inlineStr">
@@ -4143,14 +4645,10 @@
           <t>הכנות שישי</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>רותם דרור</t>
-        </is>
-      </c>
+      <c r="C3" s="19" t="n"/>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>רותם דרור, ארבל פרנקו, יונתן לירז</t>
+          <t>רגב שהם, איתן כהן, ירדן בן שחר, טליה קור, יהב לוי</t>
         </is>
       </c>
       <c r="E3" s="22">
@@ -4165,7 +4663,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="B4" s="27" t="inlineStr">
@@ -4173,14 +4671,10 @@
           <t>הכנות שישי</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>יותם ספיר</t>
-        </is>
-      </c>
+      <c r="C4" s="19" t="n"/>
       <c r="D4" s="30" t="inlineStr">
         <is>
-          <t>יותם ספיר, ירדן בן שחר, טליה קור</t>
+          <t>עשהאל ירושלמי, הדר עמדי, מישל דוד, משה אוברשטיין</t>
         </is>
       </c>
       <c r="E4" s="22">
@@ -4195,7 +4689,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
@@ -4203,14 +4697,10 @@
           <t>הכנות שישי</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>סהר שירון</t>
-        </is>
-      </c>
+      <c r="C5" s="19" t="n"/>
       <c r="D5" s="30" t="inlineStr">
         <is>
-          <t>סהר שירון, שחר מרקוביץ' גליק, רוני כהן</t>
+          <t>שירה אדלה לוזון, זואי כהן, אלה גוטליב, יונתן לירז</t>
         </is>
       </c>
       <c r="E5" s="22">
@@ -4225,7 +4715,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>עוגות · צוות שילת</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
@@ -4233,14 +4723,10 @@
           <t>הכנות שישי</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>שילת פילפל</t>
-        </is>
-      </c>
+      <c r="C6" s="19" t="n"/>
       <c r="D6" s="30" t="inlineStr">
         <is>
-          <t>שילת פילפל, שירה ספונוב</t>
+          <t>איתי בן מנחם, פרת פולס</t>
         </is>
       </c>
       <c r="E6" s="22">
@@ -4255,7 +4741,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
@@ -4263,14 +4749,10 @@
           <t>הכנות שישי</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>ינון לוי</t>
-        </is>
-      </c>
+      <c r="C7" s="19" t="n"/>
       <c r="D7" s="30" t="inlineStr">
         <is>
-          <t>ינון לוי, שי- לי וולגמוט, עשהאל ירושלמי, של״ו רובינשטיין</t>
+          <t>שחר מרקוביץ' גליק, עמרי קולטון</t>
         </is>
       </c>
       <c r="E7" s="22">
@@ -4285,18 +4767,18 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="C8" s="19" t="n"/>
       <c r="D8" s="30" t="inlineStr">
         <is>
-          <t>יהונתן קצב, פרת פולס, יהב לוי, עמית שי אברהם, איתי בן מנחם, איתן כהן</t>
+          <t>איתן וינסטון, יעל שם טוב</t>
         </is>
       </c>
       <c r="E8" s="22">
@@ -4311,18 +4793,18 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>סלט חצילים</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="C9" s="19" t="n"/>
       <c r="D9" s="30" t="inlineStr">
         <is>
-          <t>שליו שישו, פנחס אליהו גלוסקין, אביב רוזנטל, נועם ישראל קומפאס, יעל שם טוב</t>
+          <t>חיים שמאי, אלרואי גרינברג</t>
         </is>
       </c>
       <c r="E9" s="22">
@@ -4337,18 +4819,18 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="C10" s="19" t="n"/>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>איתי רוס, עמרי קולטון, יובל יצחק, אורי אסף, זואי כהן</t>
+          <t>ליבי בוכריס, רוני כהן</t>
         </is>
       </c>
       <c r="E10" s="22">
@@ -4360,11 +4842,23 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="18" t="n"/>
-      <c r="B11" s="27" t="n"/>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
       <c r="C11" s="19" t="n"/>
-      <c r="D11" s="30" t="n"/>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>אנה עזריאל, של״ו רובינשטיין, ארבל פרנקו, עופר בביוף, אורי אסף, עמית שי אברהם, הילי אלפסי, שליו שישו, תמר פרידמן, יהונתן קצב, איתי רוס, עומר יוסף גנון, אלה מאיר, פנחס אליהו גלוסקין, שירה ספונוב, נגה חוה כהן</t>
+        </is>
+      </c>
       <c r="E11" s="22">
         <f>IF(D11="","",LEN(D11)-LEN(SUBSTITUTE(D11,",",""))+1)</f>
         <v/>
@@ -4374,11 +4868,23 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="n"/>
-      <c r="B12" s="27" t="n"/>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
       <c r="C12" s="19" t="n"/>
-      <c r="D12" s="30" t="n"/>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
+        </is>
+      </c>
       <c r="E12" s="22">
         <f>IF(D12="","",LEN(D12)-LEN(SUBSTITUTE(D12,",",""))+1)</f>
         <v/>
@@ -4388,11 +4894,23 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="18" t="n"/>
-      <c r="B13" s="27" t="n"/>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
       <c r="C13" s="19" t="n"/>
-      <c r="D13" s="30" t="n"/>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>רותם דרור, אחיה נחמני, מישל דוד, זואי כהן, נגה שוהם</t>
+        </is>
+      </c>
       <c r="E13" s="22">
         <f>IF(D13="","",LEN(D13)-LEN(SUBSTITUTE(D13,",",""))+1)</f>
         <v/>
@@ -4402,11 +4920,23 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="27" t="n"/>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
       <c r="C14" s="19" t="n"/>
-      <c r="D14" s="30" t="n"/>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>שירה אדלה לוזון, טליה קור, רוני פרנקל, אלה גוטליב, הדר עמדי</t>
+        </is>
+      </c>
       <c r="E14" s="22">
         <f>IF(D14="","",LEN(D14)-LEN(SUBSTITUTE(D14,",",""))+1)</f>
         <v/>
@@ -4803,7 +5333,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n"/>
+      <c r="D4" s="34" t="inlineStr">
+        <is>
+          <t>בראוניז ללא גלוטן</t>
+        </is>
+      </c>
       <c r="E4" s="22">
         <f>IF(A4="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A4&amp;"*"))</f>
         <v/>
@@ -4836,7 +5370,7 @@
       </c>
       <c r="D5" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E5" s="22">
@@ -4869,7 +5403,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D6" s="34" t="n"/>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E6" s="22">
         <f>IF(A6="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A6&amp;"*"))</f>
         <v/>
@@ -4902,7 +5440,7 @@
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E7" s="22">
@@ -4968,7 +5506,7 @@
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E9" s="22">
@@ -5001,7 +5539,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D10" s="34" t="n"/>
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
       <c r="E10" s="22">
         <f>IF(A10="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A10&amp;"*"))</f>
         <v/>
@@ -5096,7 +5638,7 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="E13" s="22">
@@ -5191,7 +5733,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D16" s="34" t="n"/>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>עוגות שמרים</t>
+        </is>
+      </c>
       <c r="E16" s="22">
         <f>IF(A16="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A16&amp;"*"))</f>
         <v/>
@@ -5255,7 +5801,7 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E18" s="22">
@@ -5290,7 +5836,7 @@
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E19" s="22">
@@ -5354,7 +5900,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D21" s="34" t="n"/>
+      <c r="D21" s="34" t="inlineStr">
+        <is>
+          <t>עוגות שמרים; בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
       <c r="E21" s="22">
         <f>IF(A21="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A21&amp;"*"))</f>
         <v/>
@@ -5447,7 +5997,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D24" s="34" t="n"/>
+      <c r="D24" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E24" s="22">
         <f>IF(A24="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A24&amp;"*"))</f>
         <v/>
@@ -5542,7 +6096,7 @@
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E27" s="22">
@@ -5577,7 +6131,7 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E28" s="22">
@@ -5610,7 +6164,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D29" s="34" t="n"/>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>סלט חצילים</t>
+        </is>
+      </c>
       <c r="E29" s="22">
         <f>IF(A29="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A29&amp;"*"))</f>
         <v/>
@@ -5641,7 +6199,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D30" s="34" t="n"/>
+      <c r="D30" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E30" s="22">
         <f>IF(A30="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A30&amp;"*"))</f>
         <v/>
@@ -5672,7 +6234,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D31" s="34" t="n"/>
+      <c r="D31" s="34" t="inlineStr">
+        <is>
+          <t>סלט חצילים</t>
+        </is>
+      </c>
       <c r="E31" s="22">
         <f>IF(A31="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A31&amp;"*"))</f>
         <v/>
@@ -5703,7 +6269,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D32" s="34" t="n"/>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t>מטבוחה; בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
       <c r="E32" s="22">
         <f>IF(A32="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A32&amp;"*"))</f>
         <v/>
@@ -5736,7 +6306,7 @@
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="E33" s="22">
@@ -5769,7 +6339,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D34" s="34" t="n"/>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E34" s="22">
         <f>IF(A34="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A34&amp;"*"))</f>
         <v/>
@@ -5800,11 +6374,7 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
-        <is>
-          <t>עוגות · צוות סהר</t>
-        </is>
-      </c>
+      <c r="D35" s="34" t="n"/>
       <c r="E35" s="22">
         <f>IF(A35="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A35&amp;"*"))</f>
         <v/>
@@ -5837,7 +6407,7 @@
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות שילת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E36" s="22">
@@ -5870,7 +6440,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D37" s="34" t="n"/>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
       <c r="E37" s="22">
         <f>IF(A37="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A37&amp;"*"))</f>
         <v/>
@@ -5901,7 +6475,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D38" s="34" t="n"/>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>עוגות שמרים; בית מדרש · קידוש</t>
+        </is>
+      </c>
       <c r="E38" s="22">
         <f>IF(A38="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A38&amp;"*"))</f>
         <v/>
@@ -5965,7 +6543,7 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E40" s="22">
@@ -5998,7 +6576,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D41" s="34" t="n"/>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E41" s="22">
         <f>IF(A41="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A41&amp;"*"))</f>
         <v/>
@@ -6060,7 +6642,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D43" s="34" t="n"/>
+      <c r="D43" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
       <c r="E43" s="22">
         <f>IF(A43="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A43&amp;"*"))</f>
         <v/>
@@ -6091,11 +6677,7 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שישי</t>
-        </is>
-      </c>
+      <c r="D44" s="34" t="n"/>
       <c r="E44" s="22">
         <f>IF(A44="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A44&amp;"*"))</f>
         <v/>
@@ -6157,7 +6739,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D46" s="34" t="n"/>
+      <c r="D46" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E46" s="22">
         <f>IF(A46="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A46&amp;"*"))</f>
         <v/>
@@ -6190,7 +6776,7 @@
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>מטבוחה; בית מדרש · קידוש</t>
         </is>
       </c>
       <c r="E47" s="22">
@@ -6225,7 +6811,7 @@
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E48" s="22">
@@ -6289,7 +6875,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D50" s="34" t="n"/>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
       <c r="E50" s="22">
         <f>IF(A50="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A50&amp;"*"))</f>
         <v/>
@@ -6384,7 +6974,7 @@
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E53" s="22">
@@ -6481,7 +7071,7 @@
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E56" s="22">
@@ -6576,7 +7166,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D59" s="34" t="n"/>
+      <c r="D59" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
       <c r="E59" s="22">
         <f>IF(A59="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A59&amp;"*"))</f>
         <v/>
@@ -6607,11 +7201,7 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
-        <is>
-          <t>עוגות · צוות יותם</t>
-        </is>
-      </c>
+      <c r="D60" s="34" t="n"/>
       <c r="E60" s="22">
         <f>IF(A60="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A60&amp;"*"))</f>
         <v/>
@@ -6642,7 +7232,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D61" s="34" t="n"/>
+      <c r="D61" s="34" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
       <c r="E61" s="22">
         <f>IF(A61="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A61&amp;"*"))</f>
         <v/>
@@ -6673,11 +7267,7 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים שישי</t>
-        </is>
-      </c>
+      <c r="D62" s="34" t="n"/>
       <c r="E62" s="22">
         <f>IF(A62="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A62&amp;"*"))</f>
         <v/>
@@ -6710,7 +7300,7 @@
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E63" s="22">
@@ -6743,11 +7333,7 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>עוגות · צוות שילת</t>
-        </is>
-      </c>
+      <c r="D64" s="34" t="n"/>
       <c r="E64" s="22">
         <f>IF(A64="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A64&amp;"*"))</f>
         <v/>
@@ -6780,7 +7366,7 @@
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E65" s="22">
@@ -6844,7 +7430,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D67" s="34" t="n"/>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>מטבוחה; בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
       <c r="E67" s="22">
         <f>IF(A67="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A67&amp;"*"))</f>
         <v/>
@@ -6877,7 +7467,7 @@
       </c>
       <c r="D68" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E68" s="22">
@@ -6943,7 +7533,7 @@
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגת דבש; בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E70" s="22">
@@ -7009,7 +7599,7 @@
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>חלות; בית מדרש · צהריים בשבת</t>
         </is>
       </c>
       <c r="E72" s="22">
@@ -7075,7 +7665,7 @@
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E74" s="22">
@@ -7141,7 +7731,7 @@
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E76" s="22">
@@ -7207,7 +7797,7 @@
       </c>
       <c r="D78" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E78" s="22">
@@ -7395,7 +7985,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D84" s="34" t="n"/>
+      <c r="D84" s="34" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שישי</t>
+        </is>
+      </c>
       <c r="E84" s="22">
         <f>IF(A84="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A84&amp;"*"))</f>
         <v/>
@@ -7614,7 +8208,7 @@
       </c>
       <c r="D91" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E91" s="22">
@@ -7649,7 +8243,7 @@
       </c>
       <c r="D92" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="E92" s="22">
@@ -7682,7 +8276,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D93" s="34" t="n"/>
+      <c r="D93" s="34" t="inlineStr">
+        <is>
+          <t>חלות</t>
+        </is>
+      </c>
       <c r="E93" s="22">
         <f>IF(A93="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A93&amp;"*"))</f>
         <v/>
@@ -7715,7 +8313,7 @@
       </c>
       <c r="D94" s="34" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="E94" s="22">
@@ -8484,7 +9082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10192,7 +10790,7 @@
       </c>
       <c r="B62" s="44" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="C62" s="45" t="inlineStr">
@@ -10207,7 +10805,7 @@
       </c>
       <c r="E62" s="44" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
+          <t>הכנת החומוס</t>
         </is>
       </c>
       <c r="F62" s="45" t="n">
@@ -10220,7 +10818,7 @@
       </c>
       <c r="B63" s="44" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="C63" s="45" t="inlineStr">
@@ -10235,7 +10833,7 @@
       </c>
       <c r="E63" s="44" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>הגשת ארוחת הצהריים</t>
         </is>
       </c>
       <c r="F63" s="45" t="n">
@@ -10248,7 +10846,7 @@
       </c>
       <c r="B64" s="44" t="inlineStr">
         <is>
-          <t>עשהאל ירושלמי</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="C64" s="45" t="inlineStr">
@@ -10263,7 +10861,7 @@
       </c>
       <c r="E64" s="44" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
+          <t>קיפול הארוחה, שטיפת כלים</t>
         </is>
       </c>
       <c r="F64" s="45" t="n">
@@ -10276,7 +10874,7 @@
       </c>
       <c r="B65" s="44" t="inlineStr">
         <is>
-          <t>עשהאל ירושלמי</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C65" s="45" t="inlineStr">
@@ -10291,7 +10889,7 @@
       </c>
       <c r="E65" s="44" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>הכנת החומוס</t>
         </is>
       </c>
       <c r="F65" s="45" t="n">
@@ -10304,7 +10902,7 @@
       </c>
       <c r="B66" s="44" t="inlineStr">
         <is>
-          <t>שי- לי וולגמוט</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C66" s="45" t="inlineStr">
@@ -10332,7 +10930,7 @@
       </c>
       <c r="B67" s="44" t="inlineStr">
         <is>
-          <t>שי- לי וולגמוט</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C67" s="45" t="inlineStr">
@@ -10360,7 +10958,7 @@
       </c>
       <c r="B68" s="44" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C68" s="45" t="inlineStr">
@@ -10370,12 +10968,12 @@
       </c>
       <c r="D68" s="44" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="E68" s="44" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
+          <t>המסה, ערבוב ואפייה</t>
         </is>
       </c>
       <c r="F68" s="45" t="n">
@@ -10388,7 +10986,7 @@
       </c>
       <c r="B69" s="44" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>יעל שם טוב</t>
         </is>
       </c>
       <c r="C69" s="45" t="inlineStr">
@@ -10398,12 +10996,12 @@
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="E69" s="44" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>המסה, ערבוב ואפייה</t>
         </is>
       </c>
       <c r="F69" s="45" t="n">
@@ -10416,7 +11014,7 @@
       </c>
       <c r="B70" s="44" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C70" s="45" t="inlineStr">
@@ -10426,12 +11024,12 @@
       </c>
       <c r="D70" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E70" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F70" s="45" t="n">
@@ -10444,7 +11042,7 @@
       </c>
       <c r="B71" s="44" t="inlineStr">
         <is>
-          <t>יותם ספיר</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C71" s="45" t="inlineStr">
@@ -10454,12 +11052,12 @@
       </c>
       <c r="D71" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E71" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F71" s="45" t="n">
@@ -10472,7 +11070,7 @@
       </c>
       <c r="B72" s="44" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="C72" s="45" t="inlineStr">
@@ -10482,12 +11080,12 @@
       </c>
       <c r="D72" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות יותם</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E72" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F72" s="45" t="n">
@@ -10500,7 +11098,7 @@
       </c>
       <c r="B73" s="44" t="inlineStr">
         <is>
-          <t>סהר שירון</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C73" s="45" t="inlineStr">
@@ -10510,12 +11108,12 @@
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E73" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F73" s="45" t="n">
@@ -10528,7 +11126,7 @@
       </c>
       <c r="B74" s="44" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C74" s="45" t="inlineStr">
@@ -10538,12 +11136,12 @@
       </c>
       <c r="D74" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E74" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>לישה, התפחה, קליעה ואפייה</t>
         </is>
       </c>
       <c r="F74" s="45" t="n">
@@ -10556,7 +11154,7 @@
       </c>
       <c r="B75" s="44" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C75" s="45" t="inlineStr">
@@ -10566,12 +11164,12 @@
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות סהר</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E75" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בישול ארוך עד מרקם ריבתי</t>
         </is>
       </c>
       <c r="F75" s="45" t="n">
@@ -10584,7 +11182,7 @@
       </c>
       <c r="B76" s="44" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C76" s="45" t="inlineStr">
@@ -10594,12 +11192,12 @@
       </c>
       <c r="D76" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E76" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בישול ארוך עד מרקם ריבתי</t>
         </is>
       </c>
       <c r="F76" s="45" t="n">
@@ -10622,12 +11220,12 @@
       </c>
       <c r="D77" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E77" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בישול ארוך עד מרקם ריבתי</t>
         </is>
       </c>
       <c r="F77" s="45" t="n">
@@ -10640,7 +11238,7 @@
       </c>
       <c r="B78" s="44" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>שירה אדלה לוזון</t>
         </is>
       </c>
       <c r="C78" s="45" t="inlineStr">
@@ -10650,12 +11248,12 @@
       </c>
       <c r="D78" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות רותם</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E78" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>בישול ארוך עד מרקם ריבתי</t>
         </is>
       </c>
       <c r="F78" s="45" t="n">
@@ -10668,7 +11266,7 @@
       </c>
       <c r="B79" s="44" t="inlineStr">
         <is>
-          <t>שילת פילפל</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C79" s="45" t="inlineStr">
@@ -10678,12 +11276,12 @@
       </c>
       <c r="D79" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות שילת</t>
+          <t>סלט חצילים</t>
         </is>
       </c>
       <c r="E79" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>קלייה, סינון, קיצוץ ותיבול</t>
         </is>
       </c>
       <c r="F79" s="45" t="n">
@@ -10696,7 +11294,7 @@
       </c>
       <c r="B80" s="44" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C80" s="45" t="inlineStr">
@@ -10706,12 +11304,12 @@
       </c>
       <c r="D80" s="44" t="inlineStr">
         <is>
-          <t>עוגות · צוות שילת</t>
+          <t>סלט חצילים</t>
         </is>
       </c>
       <c r="E80" s="44" t="inlineStr">
         <is>
-          <t>אפיית עוגות לפי המתכון</t>
+          <t>קלייה, סינון, קיצוץ ותיבול</t>
         </is>
       </c>
       <c r="F80" s="45" t="n">
@@ -10724,22 +11322,22 @@
       </c>
       <c r="B81" s="44" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C81" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D81" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E81" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>בצק, מילוי, קליעת קראנץ' ואפייה</t>
         </is>
       </c>
       <c r="F81" s="45" t="n">
@@ -10752,22 +11350,22 @@
       </c>
       <c r="B82" s="44" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>מישל דוד</t>
         </is>
       </c>
       <c r="C82" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D82" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E82" s="44" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>בצק, מילוי, קליעת קראנץ' ואפייה</t>
         </is>
       </c>
       <c r="F82" s="45" t="n">
@@ -10780,22 +11378,22 @@
       </c>
       <c r="B83" s="44" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C83" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D83" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E83" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>בצק, מילוי, קליעת קראנץ' ואפייה</t>
         </is>
       </c>
       <c r="F83" s="45" t="n">
@@ -10808,22 +11406,22 @@
       </c>
       <c r="B84" s="44" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>עשהאל ירושלמי</t>
         </is>
       </c>
       <c r="C84" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D84" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="E84" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>בצק, מילוי, קליעת קראנץ' ואפייה</t>
         </is>
       </c>
       <c r="F84" s="45" t="n">
@@ -10836,22 +11434,22 @@
       </c>
       <c r="B85" s="44" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>עמרי קולטון</t>
         </is>
       </c>
       <c r="C85" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D85" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E85" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>הכנת הבצק, כדרור ואפייה</t>
         </is>
       </c>
       <c r="F85" s="45" t="n">
@@ -10864,22 +11462,22 @@
       </c>
       <c r="B86" s="44" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="C86" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D86" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E86" s="44" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>הכנת הבצק, כדרור ואפייה</t>
         </is>
       </c>
       <c r="F86" s="45" t="n">
@@ -10892,22 +11490,22 @@
       </c>
       <c r="B87" s="44" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C87" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D87" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="E87" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>אפיית 10–12 תבניות אינגליש</t>
         </is>
       </c>
       <c r="F87" s="45" t="n">
@@ -10920,22 +11518,22 @@
       </c>
       <c r="B88" s="44" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>פרת פולס</t>
         </is>
       </c>
       <c r="C88" s="45" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="D88" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="E88" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>אפיית 10–12 תבניות אינגליש</t>
         </is>
       </c>
       <c r="F88" s="45" t="n">
@@ -10948,7 +11546,7 @@
       </c>
       <c r="B89" s="44" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>אביב רוזנטל</t>
         </is>
       </c>
       <c r="C89" s="45" t="inlineStr">
@@ -10963,7 +11561,7 @@
       </c>
       <c r="E89" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>הכנת סלט טחינה — חצי כמות לארוחת הערב</t>
         </is>
       </c>
       <c r="F89" s="45" t="n">
@@ -10976,7 +11574,7 @@
       </c>
       <c r="B90" s="44" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>אביב רוזנטל</t>
         </is>
       </c>
       <c r="C90" s="45" t="inlineStr">
@@ -11004,7 +11602,7 @@
       </c>
       <c r="B91" s="44" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>אביב רוזנטל</t>
         </is>
       </c>
       <c r="C91" s="45" t="inlineStr">
@@ -11032,7 +11630,7 @@
       </c>
       <c r="B92" s="44" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>אביב רוזנטל</t>
         </is>
       </c>
       <c r="C92" s="45" t="inlineStr">
@@ -11060,7 +11658,7 @@
       </c>
       <c r="B93" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C93" s="45" t="inlineStr">
@@ -11075,7 +11673,7 @@
       </c>
       <c r="E93" s="44" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F93" s="45" t="n">
@@ -11088,7 +11686,7 @@
       </c>
       <c r="B94" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C94" s="45" t="inlineStr">
@@ -11103,7 +11701,7 @@
       </c>
       <c r="E94" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
         </is>
       </c>
       <c r="F94" s="45" t="n">
@@ -11116,7 +11714,7 @@
       </c>
       <c r="B95" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C95" s="45" t="inlineStr">
@@ -11131,7 +11729,7 @@
       </c>
       <c r="E95" s="44" t="inlineStr">
         <is>
-          <t>חיתוך אבטיח</t>
+          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
         </is>
       </c>
       <c r="F95" s="45" t="n">
@@ -11144,7 +11742,7 @@
       </c>
       <c r="B96" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C96" s="45" t="inlineStr">
@@ -11159,7 +11757,7 @@
       </c>
       <c r="E96" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
         </is>
       </c>
       <c r="F96" s="45" t="n">
@@ -11172,7 +11770,7 @@
       </c>
       <c r="B97" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C97" s="45" t="inlineStr">
@@ -11187,7 +11785,7 @@
       </c>
       <c r="E97" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
         </is>
       </c>
       <c r="F97" s="45" t="n">
@@ -11200,7 +11798,7 @@
       </c>
       <c r="B98" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C98" s="45" t="inlineStr">
@@ -11215,7 +11813,7 @@
       </c>
       <c r="E98" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
         </is>
       </c>
       <c r="F98" s="45" t="n">
@@ -11228,7 +11826,7 @@
       </c>
       <c r="B99" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C99" s="45" t="inlineStr">
@@ -11243,7 +11841,7 @@
       </c>
       <c r="E99" s="44" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
         </is>
       </c>
       <c r="F99" s="45" t="n">
@@ -11256,7 +11854,7 @@
       </c>
       <c r="B100" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C100" s="45" t="inlineStr">
@@ -11271,7 +11869,7 @@
       </c>
       <c r="E100" s="44" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F100" s="45" t="n">
@@ -11284,7 +11882,7 @@
       </c>
       <c r="B101" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C101" s="45" t="inlineStr">
@@ -11312,7 +11910,7 @@
       </c>
       <c r="B102" s="44" t="inlineStr">
         <is>
-          <t>פרת פולס</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C102" s="45" t="inlineStr">
@@ -11327,7 +11925,7 @@
       </c>
       <c r="E102" s="44" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
         </is>
       </c>
       <c r="F102" s="45" t="n">
@@ -11340,7 +11938,7 @@
       </c>
       <c r="B103" s="44" t="inlineStr">
         <is>
-          <t>פרת פולס</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C103" s="45" t="inlineStr">
@@ -11355,7 +11953,7 @@
       </c>
       <c r="E103" s="44" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
         </is>
       </c>
       <c r="F103" s="45" t="n">
@@ -11368,7 +11966,7 @@
       </c>
       <c r="B104" s="44" t="inlineStr">
         <is>
-          <t>פרת פולס</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C104" s="45" t="inlineStr">
@@ -11383,7 +11981,7 @@
       </c>
       <c r="E104" s="44" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>חימום 10 עוגות פרווה על הפלטה</t>
         </is>
       </c>
       <c r="F104" s="45" t="n">
@@ -11396,7 +11994,7 @@
       </c>
       <c r="B105" s="44" t="inlineStr">
         <is>
-          <t>פרת פולס</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C105" s="45" t="inlineStr">
@@ -11411,7 +12009,7 @@
       </c>
       <c r="E105" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F105" s="45" t="n">
@@ -11424,7 +12022,7 @@
       </c>
       <c r="B106" s="44" t="inlineStr">
         <is>
-          <t>אורי אסף</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C106" s="45" t="inlineStr">
@@ -11434,12 +12032,12 @@
       </c>
       <c r="D106" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E106" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
         </is>
       </c>
       <c r="F106" s="45" t="n">
@@ -11452,7 +12050,7 @@
       </c>
       <c r="B107" s="44" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C107" s="45" t="inlineStr">
@@ -11462,12 +12060,12 @@
       </c>
       <c r="D107" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E107" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל בתנור החימום</t>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
         </is>
       </c>
       <c r="F107" s="45" t="n">
@@ -11480,7 +12078,7 @@
       </c>
       <c r="B108" s="44" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C108" s="45" t="inlineStr">
@@ -11490,12 +12088,12 @@
       </c>
       <c r="D108" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E108" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
         </is>
       </c>
       <c r="F108" s="45" t="n">
@@ -11508,7 +12106,7 @@
       </c>
       <c r="B109" s="44" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C109" s="45" t="inlineStr">
@@ -11518,12 +12116,12 @@
       </c>
       <c r="D109" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E109" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>חיתוך אבטיח</t>
         </is>
       </c>
       <c r="F109" s="45" t="n">
@@ -11546,12 +12144,12 @@
       </c>
       <c r="D110" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E110" s="44" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F110" s="45" t="n">
@@ -11564,7 +12162,7 @@
       </c>
       <c r="B111" s="44" t="inlineStr">
         <is>
-          <t>עמרי קולטון</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C111" s="45" t="inlineStr">
@@ -11574,12 +12172,12 @@
       </c>
       <c r="D111" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E111" s="44" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
         </is>
       </c>
       <c r="F111" s="45" t="n">
@@ -11592,7 +12190,7 @@
       </c>
       <c r="B112" s="44" t="inlineStr">
         <is>
-          <t>אביב רוזנטל</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C112" s="45" t="inlineStr">
@@ -11602,12 +12200,12 @@
       </c>
       <c r="D112" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E112" s="44" t="inlineStr">
         <is>
-          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+          <t>פריקת האוכל שמגיע מהקייטרינג</t>
         </is>
       </c>
       <c r="F112" s="45" t="n">
@@ -11620,7 +12218,7 @@
       </c>
       <c r="B113" s="44" t="inlineStr">
         <is>
-          <t>יעל שם טוב</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C113" s="45" t="inlineStr">
@@ -11630,12 +12228,12 @@
       </c>
       <c r="D113" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E113" s="44" t="inlineStr">
         <is>
-          <t>חיתוך האבטיח</t>
+          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F113" s="45" t="n">
@@ -11658,12 +12256,12 @@
       </c>
       <c r="D114" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E114" s="44" t="inlineStr">
         <is>
-          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
         </is>
       </c>
       <c r="F114" s="45" t="n">
@@ -11676,7 +12274,7 @@
       </c>
       <c r="B115" s="44" t="inlineStr">
         <is>
-          <t>פנחס אליהו גלוסקין</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C115" s="45" t="inlineStr">
@@ -11686,12 +12284,12 @@
       </c>
       <c r="D115" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
         </is>
       </c>
       <c r="E115" s="44" t="inlineStr">
         <is>
-          <t>חימום עוגות</t>
+          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
         </is>
       </c>
       <c r="F115" s="45" t="n">
@@ -11704,25 +12302,1313 @@
       </c>
       <c r="B116" s="44" t="inlineStr">
         <is>
+          <t>נועם ישראל קומפאס</t>
+        </is>
+      </c>
+      <c r="C116" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D116" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · ארוחת ערב וטיש</t>
+        </is>
+      </c>
+      <c r="E116" s="44" t="inlineStr">
+        <is>
+          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+        </is>
+      </c>
+      <c r="F116" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B117" s="44" t="inlineStr">
+        <is>
+          <t>אלה גוטליב</t>
+        </is>
+      </c>
+      <c r="C117" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D117" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E117" s="44" t="inlineStr">
+        <is>
+          <t>הכנת סלט טחינה — חצי כמות לארוחת הצהריים</t>
+        </is>
+      </c>
+      <c r="F117" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B118" s="44" t="inlineStr">
+        <is>
+          <t>אלה גוטליב</t>
+        </is>
+      </c>
+      <c r="C118" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D118" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E118" s="44" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="F118" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B119" s="44" t="inlineStr">
+        <is>
+          <t>הדר עמדי</t>
+        </is>
+      </c>
+      <c r="C119" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D119" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E119" s="44" t="inlineStr">
+        <is>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+        </is>
+      </c>
+      <c r="F119" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B120" s="44" t="inlineStr">
+        <is>
+          <t>טליה קור</t>
+        </is>
+      </c>
+      <c r="C120" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D120" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E120" s="44" t="inlineStr">
+        <is>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+        </is>
+      </c>
+      <c r="F120" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B121" s="44" t="inlineStr">
+        <is>
+          <t>טליה קור</t>
+        </is>
+      </c>
+      <c r="C121" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D121" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E121" s="44" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="F121" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B122" s="44" t="inlineStr">
+        <is>
+          <t>רוני פרנקל</t>
+        </is>
+      </c>
+      <c r="C122" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D122" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E122" s="44" t="inlineStr">
+        <is>
+          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+        </is>
+      </c>
+      <c r="F122" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B123" s="44" t="inlineStr">
+        <is>
+          <t>רוני פרנקל</t>
+        </is>
+      </c>
+      <c r="C123" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D123" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E123" s="44" t="inlineStr">
+        <is>
+          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+        </is>
+      </c>
+      <c r="F123" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B124" s="44" t="inlineStr">
+        <is>
+          <t>שירה אדלה לוזון</t>
+        </is>
+      </c>
+      <c r="C124" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D124" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E124" s="44" t="inlineStr">
+        <is>
+          <t>הנחת האוכל בתנור החימום</t>
+        </is>
+      </c>
+      <c r="F124" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B125" s="44" t="inlineStr">
+        <is>
+          <t>שירה אדלה לוזון</t>
+        </is>
+      </c>
+      <c r="C125" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D125" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · צהריים בשבת</t>
+        </is>
+      </c>
+      <c r="E125" s="44" t="inlineStr">
+        <is>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+        </is>
+      </c>
+      <c r="F125" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B126" s="44" t="inlineStr">
+        <is>
+          <t>אחיה נחמני</t>
+        </is>
+      </c>
+      <c r="C126" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D126" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E126" s="44" t="inlineStr">
+        <is>
+          <t>חימום עוגות</t>
+        </is>
+      </c>
+      <c r="F126" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B127" s="44" t="inlineStr">
+        <is>
+          <t>זואי כהן</t>
+        </is>
+      </c>
+      <c r="C127" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D127" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E127" s="44" t="inlineStr">
+        <is>
+          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+        </is>
+      </c>
+      <c r="F127" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B128" s="44" t="inlineStr">
+        <is>
+          <t>מישל דוד</t>
+        </is>
+      </c>
+      <c r="C128" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D128" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E128" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+        </is>
+      </c>
+      <c r="F128" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B129" s="44" t="inlineStr">
+        <is>
+          <t>נגה שוהם</t>
+        </is>
+      </c>
+      <c r="C129" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D129" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E129" s="44" t="inlineStr">
+        <is>
+          <t>חיתוך האבטיח</t>
+        </is>
+      </c>
+      <c r="F129" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B130" s="44" t="inlineStr">
+        <is>
+          <t>רותם דרור</t>
+        </is>
+      </c>
+      <c r="C130" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="D130" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש · קידוש</t>
+        </is>
+      </c>
+      <c r="E130" s="44" t="inlineStr">
+        <is>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+        </is>
+      </c>
+      <c r="F130" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B131" s="44" t="inlineStr">
+        <is>
+          <t>אורי אסף</t>
+        </is>
+      </c>
+      <c r="C131" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D131" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E131" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F131" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B132" s="44" t="inlineStr">
+        <is>
+          <t>אורי אסף</t>
+        </is>
+      </c>
+      <c r="C132" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D132" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E132" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F132" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B133" s="44" t="inlineStr">
+        <is>
+          <t>איתי רוס</t>
+        </is>
+      </c>
+      <c r="C133" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D133" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E133" s="44" t="inlineStr">
+        <is>
+          <t>תליית מחיצה</t>
+        </is>
+      </c>
+      <c r="F133" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B134" s="44" t="inlineStr">
+        <is>
+          <t>איתי רוס</t>
+        </is>
+      </c>
+      <c r="C134" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D134" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E134" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F134" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B135" s="44" t="inlineStr">
+        <is>
+          <t>אלה מאיר</t>
+        </is>
+      </c>
+      <c r="C135" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D135" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E135" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F135" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B136" s="44" t="inlineStr">
+        <is>
+          <t>אלה מאיר</t>
+        </is>
+      </c>
+      <c r="C136" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D136" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E136" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F136" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B137" s="44" t="inlineStr">
+        <is>
+          <t>אנה עזריאל</t>
+        </is>
+      </c>
+      <c r="C137" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D137" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E137" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F137" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B138" s="44" t="inlineStr">
+        <is>
+          <t>אנה עזריאל</t>
+        </is>
+      </c>
+      <c r="C138" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D138" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E138" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F138" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B139" s="44" t="inlineStr">
+        <is>
+          <t>ארבל פרנקו</t>
+        </is>
+      </c>
+      <c r="C139" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D139" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E139" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F139" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B140" s="44" t="inlineStr">
+        <is>
+          <t>ארבל פרנקו</t>
+        </is>
+      </c>
+      <c r="C140" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D140" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E140" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F140" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B141" s="44" t="inlineStr">
+        <is>
+          <t>הילי אלפסי</t>
+        </is>
+      </c>
+      <c r="C141" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D141" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E141" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת רצפה</t>
+        </is>
+      </c>
+      <c r="F141" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B142" s="44" t="inlineStr">
+        <is>
+          <t>הילי אלפסי</t>
+        </is>
+      </c>
+      <c r="C142" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D142" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E142" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F142" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B143" s="44" t="inlineStr">
+        <is>
+          <t>יהונתן קצב</t>
+        </is>
+      </c>
+      <c r="C143" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D143" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E143" s="44" t="inlineStr">
+        <is>
+          <t>תליית מחיצה</t>
+        </is>
+      </c>
+      <c r="F143" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B144" s="44" t="inlineStr">
+        <is>
+          <t>יהונתן קצב</t>
+        </is>
+      </c>
+      <c r="C144" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D144" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E144" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F144" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B145" s="44" t="inlineStr">
+        <is>
+          <t>נגה חוה כהן</t>
+        </is>
+      </c>
+      <c r="C145" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D145" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E145" s="44" t="inlineStr">
+        <is>
+          <t>הנחת סידורים על הכסאות</t>
+        </is>
+      </c>
+      <c r="F145" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B146" s="44" t="inlineStr">
+        <is>
+          <t>נגה חוה כהן</t>
+        </is>
+      </c>
+      <c r="C146" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D146" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E146" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F146" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B147" s="44" t="inlineStr">
+        <is>
+          <t>עומר יוסף גנון</t>
+        </is>
+      </c>
+      <c r="C147" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D147" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E147" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F147" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B148" s="44" t="inlineStr">
+        <is>
+          <t>עומר יוסף גנון</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D148" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E148" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F148" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B149" s="44" t="inlineStr">
+        <is>
+          <t>עופר בביוף</t>
+        </is>
+      </c>
+      <c r="C149" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D149" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E149" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F149" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B150" s="44" t="inlineStr">
+        <is>
+          <t>עופר בביוף</t>
+        </is>
+      </c>
+      <c r="C150" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D150" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E150" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F150" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B151" s="44" t="inlineStr">
+        <is>
+          <t>עמית שי אברהם</t>
+        </is>
+      </c>
+      <c r="C151" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D151" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E151" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F151" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B152" s="44" t="inlineStr">
+        <is>
+          <t>עמית שי אברהם</t>
+        </is>
+      </c>
+      <c r="C152" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D152" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E152" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F152" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B153" s="44" t="inlineStr">
+        <is>
+          <t>פנחס אליהו גלוסקין</t>
+        </is>
+      </c>
+      <c r="C153" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D153" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E153" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F153" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B154" s="44" t="inlineStr">
+        <is>
+          <t>פנחס אליהו גלוסקין</t>
+        </is>
+      </c>
+      <c r="C154" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D154" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E154" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F154" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B155" s="44" t="inlineStr">
+        <is>
+          <t>שירה ספונוב</t>
+        </is>
+      </c>
+      <c r="C155" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D155" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E155" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F155" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B156" s="44" t="inlineStr">
+        <is>
+          <t>שירה ספונוב</t>
+        </is>
+      </c>
+      <c r="C156" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D156" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E156" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F156" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B157" s="44" t="inlineStr">
+        <is>
           <t>שליו שישו</t>
         </is>
       </c>
-      <c r="C116" s="45" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="D116" s="44" t="inlineStr">
-        <is>
-          <t>בית מדרש · קידוש</t>
-        </is>
-      </c>
-      <c r="E116" s="44" t="inlineStr">
-        <is>
-          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
-        </is>
-      </c>
-      <c r="F116" s="45" t="n">
+      <c r="C157" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D157" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E157" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת רצפה</t>
+        </is>
+      </c>
+      <c r="F157" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B158" s="44" t="inlineStr">
+        <is>
+          <t>שליו שישו</t>
+        </is>
+      </c>
+      <c r="C158" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D158" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E158" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F158" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B159" s="44" t="inlineStr">
+        <is>
+          <t>של״ו רובינשטיין</t>
+        </is>
+      </c>
+      <c r="C159" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D159" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E159" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F159" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B160" s="44" t="inlineStr">
+        <is>
+          <t>של״ו רובינשטיין</t>
+        </is>
+      </c>
+      <c r="C160" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D160" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E160" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F160" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B161" s="44" t="inlineStr">
+        <is>
+          <t>תמר פרידמן</t>
+        </is>
+      </c>
+      <c r="C161" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D161" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E161" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת רצפה</t>
+        </is>
+      </c>
+      <c r="F161" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B162" s="44" t="inlineStr">
+        <is>
+          <t>תמר פרידמן</t>
+        </is>
+      </c>
+      <c r="C162" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E162" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F162" s="45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11792,77 +13678,375 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="27" t="n"/>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="27" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="20" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="n"/>
-      <c r="B4" s="18" t="n"/>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>מאפים</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>חלות</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>10 ק"ג קמח</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>10 ק"ג קמח
+200 גרם שמרים יבשים
+1 ק"ג סוכר
+1.2–1.33 ליטר שמן
+כ-5 ליטר מים פושרים
+כ-150 גרם מלח (כ-6 כפות)
+ביצים ושומשום להברשה</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>בקערות גדולות מאוד שופכים את הקמח, יוצרים גומות ושמים את השמרים והסוכר. מוסיפים בהדרגה כ-4.5 ליטר מים פושרים ומתחילים ללוש.
+מוסיפים את השמן וממשיכים ללוש. לקראת סוף הלישה מוסיפים את המלח ואת יתרת המים במידת הצורך, עד לבצק רך, גמיש ולא דביק (כ-10–12 דקות).
+משמנים מעט את פני הבצק, מכסים ומתפיחים עד להכפלת הנפח (60–90 דקות).
+מורידים אוויר, מחלקים לכדורים שווים, יוצרים רצועות וקולעים חלות.
+מניחים על תבניות עם נייר אפייה, מכסים ומתפיחים שוב 30–40 דקות.
+מברישים בביצה טרופה, מפזרים שומשום ואופים ב-180 מעלות 25–30 דקות, עד להזהבה עמוקה גם בתחתית.</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>שתי התפחות — להתחיל מוקדם</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>עוגות</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>עוגות שמרים (קראנץ' קינמון ושוקולד)</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>6–8 קראנצ'ים</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>לבצק:
+3 ק"ג קמח
+50 גרם שמרים יבשים
+3 שקיות אבקת אפייה
+400 גרם סוכר (כ-2 כוסות)
+12 ביצים
+500 מ"ל שמן
+תמצית וניל
+כ-700–900 מ"ל מים פושרים (לפי ספיגת הבצק)
+למילוי:
+1.6 ק"ג סוכר
+300 גרם קקאו
+6 כפות קינמון
+500 מ"ל שמן (למריחה וחיבור המילוי)</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>הבצק: מערבבים קמח, שמרים, אבקת אפייה ו-400 גרם סוכר. מוסיפים ביצים, תמצית וניל, שמן ומים בהדרגה. לשים כ-10 דקות לבצק רך, חלק וגמיש. מתפיחים שעה עד שעה וחצי להכפלת הנפח.
+המילוי: מערבבים את הסוכר שנותר, הקקאו והקינמון לתערובת אחידה.
+מחלקים את הבצק ל-6–8 כדורים שווים ומרדדים כל אחד למלבן דק.
+מברישים בשכבת שמן נדיבה ומפזרים שכבה אחידה ונדיבה מתערובת הסוכר-קקאו-קינמון.
+מגלגלים לרולדה מהודקת, חוצים לאורכה לשתי רצועות וקולעים לצמת בורג.
+מניחים בתבניות, מתפיחים 30 דקות נוספות, ואופים ב-175 מעלות 25–30 דקות עד להשחמה יפה.</t>
+        </is>
+      </c>
       <c r="F4" s="20" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>בישול</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>מטבוחה</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>100 עגבניות</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>100 עגבניות אדומות ובשלות (חלוטות, מקולפות וקצוצות)
+1 ק"ג עגבניות שרי (קצוצות, אם משתמשים)
+3–4 ק"ג פלפלים אדומים (קוביות קטנות או קלויים ומקולפים)
+6 פלפלים ירוקים חריפים (קצוצים דק)
+22 שיני שום פרוסות או כתושות
+1 ליטר שמן (עדיף זית)
+מלח גס לפי הטעם
+4–5 כפות פפריקה מתוקה בשמן
+מעט פפריקה חריפה</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>בסיר גדול ורחב מחממים חצי מכמות השמן (500 מ"ל) על אש בינונית. מוסיפים שום ופלפלים חריפים ומטגנים כדקה (להיזהר לא לשרוף את השום).
+מוסיפים את הפלפלים האדומים ומבשלים תוך ערבוב כ-15 דקות עד שהם מתרככים.
+מוסיפים את העגבניות הקצוצות (והשרי). מביאים לרתיחה, מנמיכים לאש נמוכה ומבשלים ללא מכסה עד שהנוזלים מצטמצמים כמעט לחלוטין (כשעתיים-שלוש).
+כשהעגבניות התפרקו והנוזלים התאדו, מוסיפים את יתרת השמן (500 מ"ל), מלח ופפריקה.
+ממשיכים לבשל על אש קטנה מאוד עוד כשעה, תוך ערבוב תכוף בתחתית, עד למרקם ריבתי מבריק והשמן נפרד וצף בצדדים.</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>בישול ארוך — כ-4 שעות בסך הכל</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>עוגות</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>עוגת דבש</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>10–12 תבניות אינגליש קייק</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>30 ביצים
+1.5 ק"ג סוכר (7.5 כוסות)
+1.8 ליטר שמן (7.5 כוסות)
+7.5 כוסות דבש
+10 כפיות גדושות קפה נמס (מומסות ב-3 כוסות מים רותחים)
+2.8 ק"ג קמח (20 כוסות)
+10 כפיות אבקת אפייה (כ-3 שקיות)
+5 כפיות סודה לשתייה
+5 כפיות קינמון</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>בקערת ערבוב ענקית טורפים היטב את הביצים עם הסוכר עד לתערובת בהירה ומעט תפוחה.
+מוסיפים בהדרגה את השמן, הדבש והקפה המומס (לוודא שאינו רותח מדי שלא יבשל את הביצים) וטורפים עד לאיחוד.
+בקערה נפרדת מערבבים את היבשים: קמח, אבקת אפייה, סודה לשתייה וקינמון.
+מוסיפים את היבשים אל הרטובים וטורפים רק עד לבלילה חלקה ללא גושים (ערבוב יתר יפגע באווריריות).
+מחלקים לתבניות אינגליש משומנות (עד 2/3 מגובה התבנית) ואופים ב-165 מעלות 35–45 דקות, עד שקיסם במרכז יוצא יבש עם פירורים לחים.</t>
+        </is>
+      </c>
       <c r="F6" s="20" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>עוגות</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>עוגיות שוקולד צ'יפס</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>כ-1.2 ק"ג קמח</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>1.2 ק"ג קמח
+1 שקית אבקת אפייה
+1 כפית סודה לשתייה
+675 גרם חמאה קרה (חתוכה לקוביות)
+540 גרם סוכר חום כהה
+300 גרם סוכר לבן
+360 גרם ביצים (כ-6–7 ביצים)
+1 כף תמצית וניל
+קורט מלח
+990 גרם שוקולד צ'יפס</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>מעבדים בקערה גדולה (או במיקסר עם וו גיטרה) את החמאה הקרה עם שני סוגי הסוכר עד לתערובת פירורית ואחידה.
+מוסיפים את הביצים בהדרגה ואת תמצית הווניל, ומערבבים עד להטמעה.
+מוסיפים קמח, אבקת אפייה, סודה לשתייה וקורט מלח, ומערבבים רק עד שמתקבל בצק אחיד (לא ללוש יותר מדי).
+מקפלים פנימה את השוקולד צ'יפס. מומלץ להכניס למקרר ל-30 דקות לייצוב.
+מכדררים כדורים בגודל כדור פינג-פונג, מניחים על תבנית מרופדת עם מרווחים נדיבים, ואופים ב-175 מעלות 10–12 דקות, עד שהשוליים זהובים והמרכז עדיין רך.</t>
+        </is>
+      </c>
       <c r="F7" s="20" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="27" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>עוגות</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>בראוניז ללא גלוטן</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>כ-600 גרם שוקולד</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>600 גרם שוקולד מריר
+660 מ"ל שמן (כ-2.75 כוסות)
+3.75 כוסות סוכר
+15 ביצים שלמות
+3 חבילות אינסטנט פודינג שוקולד או וניל ללא גלוטן</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>ממיסים את השוקולד המריר יחד עם השמן בקערה גדולה (במיקרוגל בפולסים של 30 שניות או מעל סיר מים חמים) עד לתערובת חלקה ומבריקה.
+בקערה נפרדת טורפים היטב את הביצים יחד עם הסוכר במטרפה ידנית.
+יוצקים את תערובת השוקולד והשמן אל הביצים תוך כדי טריפה מתמדת.
+מוסיפים את אבקת האינסטנט פודינג וטורפים רק עד לבלילה אחידה ללא גושים.
+יוצקים לתבניות מרופדות בנייר אפייה ואופים ב-175 מעלות 25–30 דקות. מוכן כשהשוליים יציבים והמרכז מעט רוטט ופאדג'י. מצננים לחלוטין לפני חיתוך.</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>ללא גלוטן — לוודא שכל המצרכים מסומנים</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>סלט חצילים קלויים</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>10 חצילים</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>10 חצילים שלמים
+5–7 שיני שום כתושות
+מיץ מ-4–5 לימונים
+1 כוס שמן זית (200–250 מ"ל)
+מלח לפי הטעם
+לחציל בטחינה: 1–1.5 חבילות טחינה גולמית ומעט מים</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>דוקרים כל חציל במזלג ב-2–3 מקומות וקולים על להבת גז גלויה, גריל, או בתנור על חום מקסימלי (גריל עליון) 30–40 דקות, עד שהקליפה חרוכה לחלוטין והבשר רך מאוד.
+מעבירים למסננת לכ-15 דקות לצינון ולהגרת נוזלים מרירים.
+חורצים לאורך, גורפים את בשר החציל בכף לקערה, וקוצצים גס בסכין (לא לטחון בבלנדר).
+מוסיפים שום כתוש, מיץ לימון, שמן זית ומלח ומערבבים היטב במזלג.</t>
+        </is>
+      </c>
       <c r="F9" s="20" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>4 ראשי כרוב (מלאה)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>4 ראשי כרוב (קצוצים לרצועות דקות)
+מיץ מ-4–5 לימונים
+1.25 כוסות שמן זית (250–300 מ"ל)
+כ-2 כפות מלח (לפי הטעם)
+אופציונלי: כפית שטוחה סוכר / פלפל שחור / שמיר קצוץ</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>חותכים את הכרוב לרצועות דקות ושמים בקערה גדולה מאוד.
+בצנצנת או קערה קטנה טורפים יחד שמן זית, מיץ לימון ומלח עד לאיחוד.
+יוצקים את הרוטב מעל הכרוב ומעסים את הכרוב בידיים דקה-שתיים (העיסוי מרכך את הכרוב ומחדיר את הטעמים).
+מניחים בצד כ-20 דקות לפני ההגשה, טועמים ומתקנים תיבול.</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>מכינים חצי כמות (2 כרובים) לכל ארוחה, סמוך להגשה</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>סלט טחינה ביתית</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>3–4 חבילות טחינה (מלאה)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>3–4 חבילות טחינה גולמית (או 2.5 אם הוספתם לחציל)
+מיץ מ-5–6 לימונים
+4–6 שיני שום כתושות
+מים קרים מאוד (בערך נפח הטחינה — להוסיף בהדרגה)
+מלח לפי הטעם
+2–3 כפות שמן זית לזילוף</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>יוצקים את הטחינה הגולמית לקערה גדולה.
+מוסיפים מיץ לימון, שום כתוש ומלח, ומתחילים לערבב במטרפה (התערובת תהפוך תחילה סמיכה מאוד וגושית — זה נורמלי).
+מוסיפים מים קרים בהדרגה תוך טריפה נמרצת, עד למרקם הרצוי (טחינה מסמיכה בקירור, לא להשאיר סמיכה מדי).
+טועמים ומאזנים מליחות וחמיצות.
+מעבירים לקערות הגשה ומזלפים מעט שמן זית מעל.</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>מכינים חצי כמות לכל ארוחה, סמוך להגשה</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="27" t="n"/>
@@ -12446,7 +14630,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="A3:A82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"עוגות,סלטים,מטבוחה,ארוחת צהריים שישי"</formula1>
+      <formula1>"מאפים,עוגות,סלטים,בישול,ארוחת צהריים שישי"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12831,7 +15015,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>לוח שבתות — זמני ירושלים</t>
         </is>
@@ -12865,839 +15049,839 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="n">
+      <c r="A3" s="39" t="n">
         <v>46269</v>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>נצבים, וילך</t>
         </is>
       </c>
-      <c r="C3" s="38" t="n">
+      <c r="C3" s="41" t="n">
         <v>0.7638888888888888</v>
       </c>
-      <c r="D3" s="38" t="n">
+      <c r="D3" s="41" t="n">
         <v>0.81875</v>
       </c>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>הזמנים מחושבים לירושלים (כניסה 40 דק' לפני השקיעה, צאה 40 דק' אחריה). אם הלוח שלך אומר אחרת — תקנו את השורה.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="n">
+      <c r="A4" s="39" t="n">
         <v>46276</v>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>ראש השנה</t>
         </is>
       </c>
-      <c r="C4" s="38" t="n">
+      <c r="C4" s="41" t="n">
         <v>0.7576388888888889</v>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="41" t="n">
         <v>0.8125</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="n">
+      <c r="A5" s="39" t="n">
         <v>46283</v>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>האזינו</t>
         </is>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="41" t="n">
         <v>0.7513888888888889</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="41" t="n">
         <v>0.8055555555555556</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="n">
+      <c r="A6" s="39" t="n">
         <v>46290</v>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>סוכות</t>
         </is>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="41" t="n">
         <v>0.7451388888888889</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="41" t="n">
         <v>0.7993055555555556</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="n">
+      <c r="A7" s="39" t="n">
         <v>46297</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>שמיני עצרת</t>
         </is>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="41" t="n">
         <v>0.7388888888888889</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="41" t="n">
         <v>0.7930555555555555</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="n">
+      <c r="A8" s="39" t="n">
         <v>46304</v>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>בראשית</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="41" t="n">
         <v>0.7326388888888888</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="41" t="n">
         <v>0.7875</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="n">
+      <c r="A9" s="39" t="n">
         <v>46311</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>נח</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n">
+      <c r="C9" s="41" t="n">
         <v>0.7263888888888889</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="41" t="n">
         <v>0.78125</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="n">
+      <c r="A10" s="39" t="n">
         <v>46318</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>לך לך</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n">
+      <c r="C10" s="41" t="n">
         <v>0.7215277777777778</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="41" t="n">
         <v>0.7763888888888889</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36" t="n">
+      <c r="A11" s="39" t="n">
         <v>46325</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>וירא</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n">
+      <c r="C11" s="41" t="n">
         <v>0.675</v>
       </c>
-      <c r="D11" s="38" t="n">
+      <c r="D11" s="41" t="n">
         <v>0.7298611111111111</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="36" t="n">
+      <c r="A12" s="39" t="n">
         <v>46332</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>חיי שרה</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C12" s="41" t="n">
         <v>0.6708333333333333</v>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D12" s="41" t="n">
         <v>0.7256944444444444</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="36" t="n">
+      <c r="A13" s="39" t="n">
         <v>46339</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>תולדות</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C13" s="41" t="n">
         <v>0.6673611111111111</v>
       </c>
-      <c r="D13" s="38" t="n">
+      <c r="D13" s="41" t="n">
         <v>0.7229166666666667</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="36" t="n">
+      <c r="A14" s="39" t="n">
         <v>46346</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>ויצא</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C14" s="41" t="n">
         <v>0.6652777777777777</v>
       </c>
-      <c r="D14" s="38" t="n">
+      <c r="D14" s="41" t="n">
         <v>0.7201388888888889</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="36" t="n">
+      <c r="A15" s="39" t="n">
         <v>46353</v>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>וישלח</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n">
+      <c r="C15" s="41" t="n">
         <v>0.6638888888888889</v>
       </c>
-      <c r="D15" s="38" t="n">
+      <c r="D15" s="41" t="n">
         <v>0.71875</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="36" t="n">
+      <c r="A16" s="39" t="n">
         <v>46360</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>וישב (חנוכה)</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="41" t="n">
         <v>0.6631944444444444</v>
       </c>
-      <c r="D16" s="38" t="n">
+      <c r="D16" s="41" t="n">
         <v>0.71875</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="n">
+      <c r="A17" s="39" t="n">
         <v>46367</v>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>מקץ (חנוכה)</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C17" s="41" t="n">
         <v>0.6638888888888889</v>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D17" s="41" t="n">
         <v>0.7194444444444444</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="36" t="n">
+      <c r="A18" s="39" t="n">
         <v>46374</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>ויגש</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C18" s="41" t="n">
         <v>0.6652777777777777</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="41" t="n">
         <v>0.7208333333333333</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="36" t="n">
+      <c r="A19" s="39" t="n">
         <v>46381</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>ויחי</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="41" t="n">
         <v>0.6673611111111111</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="41" t="n">
         <v>0.7236111111111111</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="36" t="n">
+      <c r="A20" s="39" t="n">
         <v>46388</v>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>שמות</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n">
+      <c r="C20" s="41" t="n">
         <v>0.6708333333333333</v>
       </c>
-      <c r="D20" s="38" t="n">
+      <c r="D20" s="41" t="n">
         <v>0.7270833333333333</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="36" t="n">
+      <c r="A21" s="39" t="n">
         <v>46395</v>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>וארא</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C21" s="41" t="n">
         <v>0.675</v>
       </c>
-      <c r="D21" s="38" t="n">
+      <c r="D21" s="41" t="n">
         <v>0.7305555555555555</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="36" t="n">
+      <c r="A22" s="39" t="n">
         <v>46402</v>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>בא</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C22" s="41" t="n">
         <v>0.6791666666666667</v>
       </c>
-      <c r="D22" s="38" t="n">
+      <c r="D22" s="41" t="n">
         <v>0.7354166666666667</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="n">
+      <c r="A23" s="39" t="n">
         <v>46409</v>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>בשלח (ט״ו בשבט)</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C23" s="41" t="n">
         <v>0.6833333333333333</v>
       </c>
-      <c r="D23" s="38" t="n">
+      <c r="D23" s="41" t="n">
         <v>0.7395833333333334</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="36" t="n">
+      <c r="A24" s="39" t="n">
         <v>46416</v>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B24" s="40" t="inlineStr">
         <is>
           <t>יתרו</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n">
+      <c r="C24" s="41" t="n">
         <v>0.6875</v>
       </c>
-      <c r="D24" s="38" t="n">
+      <c r="D24" s="41" t="n">
         <v>0.74375</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="36" t="n">
+      <c r="A25" s="39" t="n">
         <v>46423</v>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>משפטים</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n">
+      <c r="C25" s="41" t="n">
         <v>0.6923611111111111</v>
       </c>
-      <c r="D25" s="38" t="n">
+      <c r="D25" s="41" t="n">
         <v>0.7486111111111111</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="n">
+      <c r="A26" s="39" t="n">
         <v>46430</v>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>תרומה</t>
         </is>
       </c>
-      <c r="C26" s="38" t="n">
+      <c r="C26" s="41" t="n">
         <v>0.6965277777777777</v>
       </c>
-      <c r="D26" s="38" t="n">
+      <c r="D26" s="41" t="n">
         <v>0.7527777777777778</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="n">
+      <c r="A27" s="39" t="n">
         <v>46437</v>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>תצוה</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n">
+      <c r="C27" s="41" t="n">
         <v>0.7006944444444444</v>
       </c>
-      <c r="D27" s="38" t="n">
+      <c r="D27" s="41" t="n">
         <v>0.7569444444444444</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="n">
+      <c r="A28" s="39" t="n">
         <v>46444</v>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="40" t="inlineStr">
         <is>
           <t>כי תשא</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C28" s="41" t="n">
         <v>0.7041666666666667</v>
       </c>
-      <c r="D28" s="38" t="n">
+      <c r="D28" s="41" t="n">
         <v>0.7604166666666666</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="n">
+      <c r="A29" s="39" t="n">
         <v>46451</v>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
         <is>
           <t>ויקהל</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C29" s="41" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="D29" s="38" t="n">
+      <c r="D29" s="41" t="n">
         <v>0.7638888888888888</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="n">
+      <c r="A30" s="39" t="n">
         <v>46458</v>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <t>פקודי</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C30" s="41" t="n">
         <v>0.7118055555555556</v>
       </c>
-      <c r="D30" s="38" t="n">
+      <c r="D30" s="41" t="n">
         <v>0.7680555555555556</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="n">
+      <c r="A31" s="39" t="n">
         <v>46465</v>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
         <is>
           <t>ויקרא</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C31" s="41" t="n">
         <v>0.7152777777777778</v>
       </c>
-      <c r="D31" s="38" t="n">
+      <c r="D31" s="41" t="n">
         <v>0.7708333333333334</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="n">
+      <c r="A32" s="39" t="n">
         <v>46472</v>
       </c>
-      <c r="B32" s="37" t="inlineStr">
+      <c r="B32" s="40" t="inlineStr">
         <is>
           <t>צו</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n">
+      <c r="C32" s="41" t="n">
         <v>0.7597222222222222</v>
       </c>
-      <c r="D32" s="38" t="n">
+      <c r="D32" s="41" t="n">
         <v>0.8159722222222222</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="36" t="n">
+      <c r="A33" s="39" t="n">
         <v>46479</v>
       </c>
-      <c r="B33" s="37" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>שמיני</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C33" s="41" t="n">
         <v>0.7631944444444444</v>
       </c>
-      <c r="D33" s="38" t="n">
+      <c r="D33" s="41" t="n">
         <v>0.8194444444444444</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="36" t="n">
+      <c r="A34" s="39" t="n">
         <v>46486</v>
       </c>
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B34" s="40" t="inlineStr">
         <is>
           <t>תזריע</t>
         </is>
       </c>
-      <c r="C34" s="38" t="n">
+      <c r="C34" s="41" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="D34" s="38" t="n">
+      <c r="D34" s="41" t="n">
         <v>0.8222222222222222</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="36" t="n">
+      <c r="A35" s="39" t="n">
         <v>46493</v>
       </c>
-      <c r="B35" s="37" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>מצורע</t>
         </is>
       </c>
-      <c r="C35" s="38" t="n">
+      <c r="C35" s="41" t="n">
         <v>0.7701388888888889</v>
       </c>
-      <c r="D35" s="38" t="n">
+      <c r="D35" s="41" t="n">
         <v>0.8256944444444444</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="36" t="n">
+      <c r="A36" s="39" t="n">
         <v>46500</v>
       </c>
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>פסח</t>
         </is>
       </c>
-      <c r="C36" s="38" t="n">
+      <c r="C36" s="41" t="n">
         <v>0.7729166666666667</v>
       </c>
-      <c r="D36" s="38" t="n">
+      <c r="D36" s="41" t="n">
         <v>0.8291666666666667</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="n">
+      <c r="A37" s="39" t="n">
         <v>46507</v>
       </c>
-      <c r="B37" s="37" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>אחרי מות</t>
         </is>
       </c>
-      <c r="C37" s="38" t="n">
+      <c r="C37" s="41" t="n">
         <v>0.7763888888888889</v>
       </c>
-      <c r="D37" s="38" t="n">
+      <c r="D37" s="41" t="n">
         <v>0.8326388888888889</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="36" t="n">
+      <c r="A38" s="39" t="n">
         <v>46514</v>
       </c>
-      <c r="B38" s="37" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>קדושים</t>
         </is>
       </c>
-      <c r="C38" s="38" t="n">
+      <c r="C38" s="41" t="n">
         <v>0.7798611111111111</v>
       </c>
-      <c r="D38" s="38" t="n">
+      <c r="D38" s="41" t="n">
         <v>0.8361111111111111</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="36" t="n">
+      <c r="A39" s="39" t="n">
         <v>46521</v>
       </c>
-      <c r="B39" s="37" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>אמור</t>
         </is>
       </c>
-      <c r="C39" s="38" t="n">
+      <c r="C39" s="41" t="n">
         <v>0.7833333333333333</v>
       </c>
-      <c r="D39" s="38" t="n">
+      <c r="D39" s="41" t="n">
         <v>0.8395833333333333</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="36" t="n">
+      <c r="A40" s="39" t="n">
         <v>46528</v>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="40" t="inlineStr">
         <is>
           <t>בהר</t>
         </is>
       </c>
-      <c r="C40" s="38" t="n">
+      <c r="C40" s="41" t="n">
         <v>0.7868055555555555</v>
       </c>
-      <c r="D40" s="38" t="n">
+      <c r="D40" s="41" t="n">
         <v>0.8423611111111111</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="36" t="n">
+      <c r="A41" s="39" t="n">
         <v>46535</v>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>בחוקותי</t>
         </is>
       </c>
-      <c r="C41" s="38" t="n">
+      <c r="C41" s="41" t="n">
         <v>0.7895833333333333</v>
       </c>
-      <c r="D41" s="38" t="n">
+      <c r="D41" s="41" t="n">
         <v>0.8458333333333333</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="36" t="n">
+      <c r="A42" s="39" t="n">
         <v>46542</v>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>במדבר</t>
         </is>
       </c>
-      <c r="C42" s="38" t="n">
+      <c r="C42" s="41" t="n">
         <v>0.7923611111111111</v>
       </c>
-      <c r="D42" s="38" t="n">
+      <c r="D42" s="41" t="n">
         <v>0.8486111111111111</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="n">
+      <c r="A43" s="39" t="n">
         <v>46549</v>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>נשא</t>
         </is>
       </c>
-      <c r="C43" s="38" t="n">
+      <c r="C43" s="41" t="n">
         <v>0.7944444444444444</v>
       </c>
-      <c r="D43" s="38" t="n">
+      <c r="D43" s="41" t="n">
         <v>0.8506944444444444</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="n">
+      <c r="A44" s="39" t="n">
         <v>46556</v>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>בהעלותך</t>
         </is>
       </c>
-      <c r="C44" s="38" t="n">
+      <c r="C44" s="41" t="n">
         <v>0.7965277777777777</v>
       </c>
-      <c r="D44" s="38" t="n">
+      <c r="D44" s="41" t="n">
         <v>0.8520833333333333</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="n">
+      <c r="A45" s="39" t="n">
         <v>46563</v>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>שלח</t>
         </is>
       </c>
-      <c r="C45" s="38" t="n">
+      <c r="C45" s="41" t="n">
         <v>0.7972222222222223</v>
       </c>
-      <c r="D45" s="38" t="n">
+      <c r="D45" s="41" t="n">
         <v>0.8527777777777777</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="n">
+      <c r="A46" s="39" t="n">
         <v>46570</v>
       </c>
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>קרח</t>
         </is>
       </c>
-      <c r="C46" s="38" t="n">
+      <c r="C46" s="41" t="n">
         <v>0.7979166666666667</v>
       </c>
-      <c r="D46" s="38" t="n">
+      <c r="D46" s="41" t="n">
         <v>0.8534722222222222</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="n">
+      <c r="A47" s="39" t="n">
         <v>46577</v>
       </c>
-      <c r="B47" s="37" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>חקת</t>
         </is>
       </c>
-      <c r="C47" s="38" t="n">
+      <c r="C47" s="41" t="n">
         <v>0.7972222222222223</v>
       </c>
-      <c r="D47" s="38" t="n">
+      <c r="D47" s="41" t="n">
         <v>0.8520833333333333</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="n">
+      <c r="A48" s="39" t="n">
         <v>46584</v>
       </c>
-      <c r="B48" s="37" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>בלק</t>
         </is>
       </c>
-      <c r="C48" s="38" t="n">
+      <c r="C48" s="41" t="n">
         <v>0.7958333333333333</v>
       </c>
-      <c r="D48" s="38" t="n">
+      <c r="D48" s="41" t="n">
         <v>0.8506944444444444</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="n">
+      <c r="A49" s="39" t="n">
         <v>46591</v>
       </c>
-      <c r="B49" s="37" t="inlineStr">
+      <c r="B49" s="40" t="inlineStr">
         <is>
           <t>פינחס</t>
         </is>
       </c>
-      <c r="C49" s="38" t="n">
+      <c r="C49" s="41" t="n">
         <v>0.7930555555555555</v>
       </c>
-      <c r="D49" s="38" t="n">
+      <c r="D49" s="41" t="n">
         <v>0.8486111111111111</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="36" t="n">
+      <c r="A50" s="39" t="n">
         <v>46598</v>
       </c>
-      <c r="B50" s="37" t="inlineStr">
+      <c r="B50" s="40" t="inlineStr">
         <is>
           <t>מטות, מסעי</t>
         </is>
       </c>
-      <c r="C50" s="38" t="n">
+      <c r="C50" s="41" t="n">
         <v>0.7902777777777777</v>
       </c>
-      <c r="D50" s="38" t="n">
+      <c r="D50" s="41" t="n">
         <v>0.8451388888888889</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="36" t="n">
+      <c r="A51" s="39" t="n">
         <v>46605</v>
       </c>
-      <c r="B51" s="37" t="inlineStr">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>דברים</t>
         </is>
       </c>
-      <c r="C51" s="38" t="n">
+      <c r="C51" s="41" t="n">
         <v>0.7861111111111111</v>
       </c>
-      <c r="D51" s="38" t="n">
+      <c r="D51" s="41" t="n">
         <v>0.8409722222222222</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="36" t="n">
+      <c r="A52" s="39" t="n">
         <v>46612</v>
       </c>
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="40" t="inlineStr">
         <is>
           <t>ואתחנן</t>
         </is>
       </c>
-      <c r="C52" s="38" t="n">
+      <c r="C52" s="41" t="n">
         <v>0.78125</v>
       </c>
-      <c r="D52" s="38" t="n">
+      <c r="D52" s="41" t="n">
         <v>0.8361111111111111</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="36" t="n">
+      <c r="A53" s="39" t="n">
         <v>46619</v>
       </c>
-      <c r="B53" s="37" t="inlineStr">
+      <c r="B53" s="40" t="inlineStr">
         <is>
           <t>עקב</t>
         </is>
       </c>
-      <c r="C53" s="38" t="n">
+      <c r="C53" s="41" t="n">
         <v>0.7763888888888889</v>
       </c>
-      <c r="D53" s="38" t="n">
+      <c r="D53" s="41" t="n">
         <v>0.83125</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="36" t="n">
+      <c r="A54" s="39" t="n">
         <v>46626</v>
       </c>
-      <c r="B54" s="37" t="inlineStr">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>ראה</t>
         </is>
       </c>
-      <c r="C54" s="38" t="n">
+      <c r="C54" s="41" t="n">
         <v>0.7708333333333334</v>
       </c>
-      <c r="D54" s="38" t="n">
+      <c r="D54" s="41" t="n">
         <v>0.8256944444444444</v>
       </c>
     </row>

--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -24,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1826,7 +1827,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K3" s="20" t="n"/>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="27" t="inlineStr">
@@ -1873,7 +1878,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K4" s="20" t="n"/>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
@@ -1920,7 +1929,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K5" s="20" t="n"/>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
@@ -1967,7 +1980,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K6" s="20" t="n"/>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="27" t="inlineStr">
@@ -2014,7 +2031,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K7" s="20" t="n"/>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
@@ -2061,7 +2082,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K8" s="20" t="n"/>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
@@ -2108,7 +2133,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K9" s="20" t="n"/>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="27" t="inlineStr">
@@ -2151,7 +2180,11 @@
           <t>תחילת עבודה</t>
         </is>
       </c>
-      <c r="K10" s="20" t="n"/>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
@@ -2556,20 +2589,20 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F20" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס, איתמר אסנהיים</t>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד</t>
         </is>
       </c>
       <c r="H20" s="19" t="n"/>
@@ -2581,7 +2614,11 @@
           <t>הדלקת נרות</t>
         </is>
       </c>
-      <c r="K20" s="20" t="n"/>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>הגסטרונומים המסומנים 2 — שנה ב'</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="27" t="inlineStr">
@@ -2595,31 +2632,27 @@
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
+          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: פרגית בגריל, קוסקוס, לקט קוסקוס, מוקפץ טבעוני · וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
-          <t>הלל פינגולד, יובל יצחק</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>סלט כרוב מרענן</t>
-        </is>
-      </c>
+          <t>יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n"/>
       <c r="I21" s="27" t="n">
         <v>1</v>
       </c>
@@ -2628,7 +2661,11 @@
           <t>הדלקת נרות</t>
         </is>
       </c>
-      <c r="K21" s="20" t="n"/>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>הגסטרונומים המסומנים 2 — שנה ב'</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="27" t="inlineStr">
@@ -2642,37 +2679,33 @@
         </is>
       </c>
       <c r="C22" s="29" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>הכנת סלט טחינה — חצי כמות לארוחת הערב</t>
+          <t>הוצאת הגסטרונומים מתנור החימום</t>
         </is>
       </c>
       <c r="F22" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>אביב רוזנטל</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>סלט טחינה ביתית</t>
-        </is>
-      </c>
+          <t>רותם דרור, אחיה נחמני, נועם ישראל קומפאס</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="n"/>
       <c r="I22" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="19" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="K22" s="20" t="n"/>
@@ -2689,24 +2722,24 @@
         </is>
       </c>
       <c r="C23" s="29" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.8125</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="30" t="inlineStr">
         <is>
-          <t>איתי בן מנחם, נועם ישראל קומפאס</t>
+          <t>איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
         </is>
       </c>
       <c r="H23" s="19" t="n"/>
@@ -2715,7 +2748,7 @@
       </c>
       <c r="J23" s="19" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="K23" s="20" t="n"/>
@@ -2731,25 +2764,21 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>0.8125</v>
-      </c>
+      <c r="C24" s="29" t="n"/>
       <c r="D24" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
-        </is>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>3</v>
-      </c>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, הלל פינגולד, יובל יצחק</t>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם, רותם דרור, אחיה נחמני</t>
         </is>
       </c>
       <c r="H24" s="19" t="n"/>
@@ -2758,7 +2787,7 @@
       </c>
       <c r="J24" s="19" t="inlineStr">
         <is>
-          <t>קבלת שבת וערבית</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K24" s="20" t="n"/>
@@ -2775,24 +2804,24 @@
         </is>
       </c>
       <c r="C25" s="29" t="n">
-        <v>0.8125</v>
+        <v>0.875</v>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>חימום העוגות: 7 פסי עוגת דבש, 4 קראנצ'ים וחצי מהבראוניז — הכל פרווה</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="30" t="inlineStr">
         <is>
-          <t>אביב רוזנטל, איתי בן מנחם, נועם ישראל קומפאס</t>
+          <t>מישל דוד, זואי כהן</t>
         </is>
       </c>
       <c r="H25" s="19" t="n"/>
@@ -2801,7 +2830,7 @@
       </c>
       <c r="J25" s="19" t="inlineStr">
         <is>
-          <t>קבלת שבת וערבית</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K25" s="20" t="n"/>
@@ -2822,20 +2851,20 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>חיתוך 10 תפוחים</t>
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="30" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, הלל פינגולד</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="H26" s="19" t="n"/>
@@ -2844,7 +2873,7 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K26" s="20" t="n"/>
@@ -2861,24 +2890,24 @@
         </is>
       </c>
       <c r="C27" s="29" t="n">
-        <v>0.875</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>חיתוך אבטיח</t>
+          <t>פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>שירה אדלה לוזון, טליה קור, מישל דוד</t>
         </is>
       </c>
       <c r="H27" s="19" t="n"/>
@@ -2887,7 +2916,7 @@
       </c>
       <c r="J27" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K27" s="20" t="n"/>
@@ -2908,20 +2937,20 @@
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F28" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>אביב רוזנטל, איתי בן מנחם, נועם ישראל קומפאס</t>
+          <t>זואי כהן, נגה שוהם</t>
         </is>
       </c>
       <c r="H28" s="19" t="n"/>
@@ -2930,7 +2959,7 @@
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K28" s="20" t="n"/>
@@ -2946,25 +2975,21 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
-        <v>0.8958333333333334</v>
-      </c>
+      <c r="C29" s="29" t="n"/>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="n">
-        <v>3</v>
-      </c>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F29" s="27" t="n"/>
       <c r="G29" s="30" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, הלל פינגולד, יובל יצחק</t>
+          <t>מישל דוד, זואי כהן, נגה שוהם, שירה אדלה לוזון, טליה קור</t>
         </is>
       </c>
       <c r="H29" s="19" t="n"/>
@@ -2973,7 +2998,7 @@
       </c>
       <c r="J29" s="19" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>טיש בחדר אוכל</t>
         </is>
       </c>
       <c r="K29" s="20" t="n"/>
@@ -2984,26 +3009,30 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C30" s="29" t="n"/>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="D30" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="n"/>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>1</v>
+      </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
+          <t>רוני פרנקל</t>
         </is>
       </c>
       <c r="H30" s="19" t="n"/>
@@ -3012,7 +3041,7 @@
       </c>
       <c r="J30" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="K30" s="20" t="n"/>
@@ -3033,12 +3062,12 @@
       </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+          <t>חימום העוגות</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
@@ -3046,7 +3075,7 @@
       </c>
       <c r="G31" s="30" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="H31" s="19" t="n"/>
@@ -3076,12 +3105,12 @@
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>חימום עוגות</t>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
       </c>
       <c r="F32" s="27" t="n">
@@ -3089,7 +3118,7 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="H32" s="19" t="n"/>
@@ -3119,12 +3148,12 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+          <t>הוצאת העוגות: 4 פסי עוגת דבש, 3 קראנצ'ים, העוגיות וחצי מהבראוניז</t>
         </is>
       </c>
       <c r="F33" s="27" t="n">
@@ -3132,7 +3161,7 @@
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>מישל דוד</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="H33" s="19" t="n"/>
@@ -3162,12 +3191,12 @@
       </c>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+          <t>הוצאת חלב, קורנפלקס וחצי מהענבים</t>
         </is>
       </c>
       <c r="F34" s="27" t="n">
@@ -3175,7 +3204,7 @@
       </c>
       <c r="G34" s="30" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="H34" s="19" t="n"/>
@@ -3201,24 +3230,24 @@
         </is>
       </c>
       <c r="C35" s="29" t="n">
-        <v>0.4375</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>חיתוך האבטיח</t>
+          <t>הכנסת האוכל לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F35" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>משה אוברשטיין, יואב אוחנה</t>
         </is>
       </c>
       <c r="H35" s="19" t="n"/>
@@ -3230,7 +3259,11 @@
           <t>קידוש</t>
         </is>
       </c>
-      <c r="K35" s="20" t="n"/>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>הגסטרונומים המסומנים 2 — שנה ב'</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="27" t="inlineStr">
@@ -3244,24 +3277,24 @@
         </is>
       </c>
       <c r="C36" s="29" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>הנחת האוכל בתנור החימום</t>
+          <t>עריכת השולחן: הכנת סלט כרוב וסלט טחינה, והוצאת סלט חצילים, מטבוחה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס) וחלות</t>
         </is>
       </c>
       <c r="F36" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>שירה אדלה לוזון</t>
+          <t>שילת פילפל, יונתן לירז, חיים שמאי</t>
         </is>
       </c>
       <c r="H36" s="19" t="n"/>
@@ -3270,10 +3303,14 @@
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
-        </is>
-      </c>
-      <c r="K36" s="20" t="n"/>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="K36" s="20" t="inlineStr">
+        <is>
+          <t>לוודא שהכל של שנה ב'</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="27" t="inlineStr">
@@ -3287,16 +3324,16 @@
         </is>
       </c>
       <c r="C37" s="29" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם, וסידור שולחנות וכיסאות</t>
         </is>
       </c>
       <c r="F37" s="27" t="n">
@@ -3304,20 +3341,16 @@
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
-          <t>טליה קור, רוני פרנקל</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="inlineStr">
-        <is>
-          <t>סלט כרוב מרענן</t>
-        </is>
-      </c>
+          <t>משה אוברשטיין, יואב אוחנה</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n"/>
       <c r="I37" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="K37" s="20" t="n"/>
@@ -3333,38 +3366,30 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
-        <v>0.4583333333333333</v>
-      </c>
+      <c r="C38" s="29" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>הכנת סלט טחינה — חצי כמות לארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="F38" s="27" t="n">
-        <v>1</v>
-      </c>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
       <c r="G38" s="30" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
-        </is>
-      </c>
-      <c r="H38" s="19" t="inlineStr">
-        <is>
-          <t>סלט טחינה ביתית</t>
-        </is>
-      </c>
+          <t>משה אוברשטיין, יואב אוחנה, שילת פילפל, יונתן לירז, חיים שמאי</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="n"/>
       <c r="I38" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="19" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="K38" s="20" t="n"/>
@@ -3375,115 +3400,55 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C39" s="29" t="n">
-        <v>0.5208333333333334</v>
-      </c>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="19" t="n"/>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
-        </is>
-      </c>
-      <c r="F39" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="30" t="inlineStr">
-        <is>
-          <t>הדר עמדי, שירה אדלה לוזון</t>
-        </is>
-      </c>
+          <t>כולם בבית המדרש לחלוקת גזרות</t>
+        </is>
+      </c>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="30" t="n"/>
       <c r="H39" s="19" t="n"/>
       <c r="I39" s="27" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="19" t="inlineStr">
         <is>
-          <t>חבורות</t>
+          <t>ניקיונות מוצ"ש</t>
         </is>
       </c>
       <c r="K39" s="20" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B40" s="31" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C40" s="29" t="n">
-        <v>0.5208333333333334</v>
-      </c>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>בית מדרש · צהריים בשבת</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
-        </is>
-      </c>
-      <c r="F40" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" s="30" t="inlineStr">
-        <is>
-          <t>טליה קור, רוני פרנקל, אלה גוטליב</t>
-        </is>
-      </c>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="27" t="n"/>
+      <c r="B40" s="27" t="n"/>
+      <c r="C40" s="29" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="30" t="n"/>
       <c r="H40" s="19" t="n"/>
-      <c r="I40" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>חבורות</t>
-        </is>
-      </c>
+      <c r="I40" s="27" t="n"/>
+      <c r="J40" s="19" t="n"/>
       <c r="K40" s="20" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="27" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B41" s="32" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="27" t="n"/>
+      <c r="B41" s="27" t="n"/>
       <c r="C41" s="29" t="n"/>
       <c r="D41" s="19" t="n"/>
-      <c r="E41" s="20" t="inlineStr">
-        <is>
-          <t>כולם בבית המדרש לחלוקת גזרות</t>
-        </is>
-      </c>
+      <c r="E41" s="20" t="n"/>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="30" t="n"/>
       <c r="H41" s="19" t="n"/>
-      <c r="I41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="19" t="inlineStr">
-        <is>
-          <t>ניקיונות מוצ"ש</t>
-        </is>
-      </c>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="19" t="n"/>
       <c r="K41" s="20" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -4871,7 +4836,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
@@ -4882,7 +4847,7 @@
       <c r="C12" s="19" t="n"/>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם</t>
+          <t>נועם ישראל קומפאס, איתמר אסנהיים, הלל פינגולד, יובל יצחק, אביב רוזנטל, איתי בן מנחם, רותם דרור, אחיה נחמני</t>
         </is>
       </c>
       <c r="E12" s="22">
@@ -4897,7 +4862,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
@@ -4908,7 +4873,7 @@
       <c r="C13" s="19" t="n"/>
       <c r="D13" s="30" t="inlineStr">
         <is>
-          <t>רותם דרור, אחיה נחמני, מישל דוד, זואי כהן, נגה שוהם</t>
+          <t>מישל דוד, זואי כהן, נגה שוהם, שירה אדלה לוזון, טליה קור</t>
         </is>
       </c>
       <c r="E13" s="22">
@@ -4923,7 +4888,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -4934,7 +4899,7 @@
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="30" t="inlineStr">
         <is>
-          <t>שירה אדלה לוזון, טליה קור, רוני פרנקל, אלה גוטליב, הדר עמדי</t>
+          <t>רוני פרנקל, אלה גוטליב, הדר עמדי, קובי סמייסון, איתן וינסטון</t>
         </is>
       </c>
       <c r="E14" s="22">
@@ -4946,11 +4911,23 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="18" t="n"/>
-      <c r="B15" s="27" t="n"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
       <c r="C15" s="19" t="n"/>
-      <c r="D15" s="30" t="n"/>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>משה אוברשטיין, יואב אוחנה, שילת פילפל, יונתן לירז, חיים שמאי</t>
+        </is>
+      </c>
       <c r="E15" s="22">
         <f>IF(D15="","",LEN(D15)-LEN(SUBSTITUTE(D15,",",""))+1)</f>
         <v/>
@@ -5335,7 +5312,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן</t>
+          <t>בראוניז ללא גלוטן; קידוש</t>
         </is>
       </c>
       <c r="E4" s="22">
@@ -5370,7 +5347,7 @@
       </c>
       <c r="D5" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E5" s="22">
@@ -5541,7 +5518,7 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E10" s="22">
@@ -5735,7 +5712,7 @@
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>עוגות שמרים</t>
+          <t>עוגות שמרים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E16" s="22">
@@ -5801,7 +5778,7 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>מטבוחה; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E18" s="22">
@@ -5902,7 +5879,7 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>עוגות שמרים; בית מדרש · צהריים בשבת</t>
+          <t>עוגות שמרים; קידוש</t>
         </is>
       </c>
       <c r="E21" s="22">
@@ -5935,7 +5912,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D22" s="34" t="n"/>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
       <c r="E22" s="22">
         <f>IF(A22="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A22&amp;"*"))</f>
         <v/>
@@ -6166,7 +6147,7 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>סלט חצילים</t>
+          <t>סלט חצילים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E29" s="22">
@@ -6271,7 +6252,7 @@
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; בית מדרש · צהריים בשבת</t>
+          <t>מטבוחה; קידוש</t>
         </is>
       </c>
       <c r="E32" s="22">
@@ -6306,7 +6287,7 @@
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E33" s="22">
@@ -6442,7 +6423,7 @@
       </c>
       <c r="D37" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E37" s="22">
@@ -6477,7 +6458,7 @@
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>עוגות שמרים; בית מדרש · קידוש</t>
+          <t>עוגות שמרים; טיש</t>
         </is>
       </c>
       <c r="E38" s="22">
@@ -6611,7 +6592,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D42" s="34" t="n"/>
+      <c r="D42" s="34" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
       <c r="E42" s="22">
         <f>IF(A42="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A42&amp;"*"))</f>
         <v/>
@@ -6644,7 +6629,7 @@
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E43" s="22">
@@ -6776,7 +6761,7 @@
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; בית מדרש · קידוש</t>
+          <t>מטבוחה; טיש</t>
         </is>
       </c>
       <c r="E47" s="22">
@@ -6877,7 +6862,7 @@
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E50" s="22">
@@ -7234,7 +7219,7 @@
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E61" s="22">
@@ -7333,7 +7318,11 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="D64" s="34" t="n"/>
+      <c r="D64" s="34" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שבת</t>
+        </is>
+      </c>
       <c r="E64" s="22">
         <f>IF(A64="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A64&amp;"*"))</f>
         <v/>
@@ -7366,7 +7355,7 @@
       </c>
       <c r="D65" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E65" s="22">
@@ -7432,7 +7421,7 @@
       </c>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; בית מדרש · צהריים בשבת</t>
+          <t>מטבוחה; טיש</t>
         </is>
       </c>
       <c r="E67" s="22">
@@ -7533,7 +7522,7 @@
       </c>
       <c r="D70" s="34" t="inlineStr">
         <is>
-          <t>עוגת דבש; בית מדרש · ארוחת ערב וטיש</t>
+          <t>עוגת דבש; ארוחת ערב</t>
         </is>
       </c>
       <c r="E70" s="22">
@@ -7599,7 +7588,7 @@
       </c>
       <c r="D72" s="34" t="inlineStr">
         <is>
-          <t>חלות; בית מדרש · צהריים בשבת</t>
+          <t>חלות; טיש</t>
         </is>
       </c>
       <c r="E72" s="22">
@@ -7665,7 +7654,7 @@
       </c>
       <c r="D74" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E74" s="22">
@@ -9082,7 +9071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11556,12 +11545,12 @@
       </c>
       <c r="D89" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E89" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט טחינה — חצי כמות לארוחת הערב</t>
+          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: פרגית בגריל, קוסקוס, לקט קוסקוס, מוקפץ טבעוני · וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F89" s="45" t="n">
@@ -11584,12 +11573,12 @@
       </c>
       <c r="D90" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E90" s="44" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F90" s="45" t="n">
@@ -11612,12 +11601,12 @@
       </c>
       <c r="D91" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E91" s="44" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F91" s="45" t="n">
@@ -11630,7 +11619,7 @@
       </c>
       <c r="B92" s="44" t="inlineStr">
         <is>
-          <t>אביב רוזנטל</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C92" s="45" t="inlineStr">
@@ -11640,12 +11629,12 @@
       </c>
       <c r="D92" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E92" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>הוצאת הגסטרונומים מתנור החימום</t>
         </is>
       </c>
       <c r="F92" s="45" t="n">
@@ -11658,7 +11647,7 @@
       </c>
       <c r="B93" s="44" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C93" s="45" t="inlineStr">
@@ -11668,12 +11657,12 @@
       </c>
       <c r="D93" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E93" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F93" s="45" t="n">
@@ -11696,12 +11685,12 @@
       </c>
       <c r="D94" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E94" s="44" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: פרגית בגריל, קוסקוס, לקט קוסקוס, מוקפץ טבעוני · וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F94" s="45" t="n">
@@ -11724,12 +11713,12 @@
       </c>
       <c r="D95" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E95" s="44" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F95" s="45" t="n">
@@ -11752,12 +11741,12 @@
       </c>
       <c r="D96" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E96" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F96" s="45" t="n">
@@ -11780,12 +11769,12 @@
       </c>
       <c r="D97" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E97" s="44" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F97" s="45" t="n">
@@ -11808,12 +11797,12 @@
       </c>
       <c r="D98" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E98" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F98" s="45" t="n">
@@ -11836,12 +11825,12 @@
       </c>
       <c r="D99" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E99" s="44" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F99" s="45" t="n">
@@ -11854,7 +11843,7 @@
       </c>
       <c r="B100" s="44" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C100" s="45" t="inlineStr">
@@ -11864,12 +11853,12 @@
       </c>
       <c r="D100" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E100" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F100" s="45" t="n">
@@ -11882,7 +11871,7 @@
       </c>
       <c r="B101" s="44" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C101" s="45" t="inlineStr">
@@ -11892,12 +11881,12 @@
       </c>
       <c r="D101" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E101" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F101" s="45" t="n">
@@ -11920,12 +11909,12 @@
       </c>
       <c r="D102" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E102" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F102" s="45" t="n">
@@ -11938,7 +11927,7 @@
       </c>
       <c r="B103" s="44" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C103" s="45" t="inlineStr">
@@ -11948,12 +11937,12 @@
       </c>
       <c r="D103" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E103" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: פרגית בגריל, קוסקוס, לקט קוסקוס, מוקפץ טבעוני · וחיבור מיחמים בפינת קפה</t>
         </is>
       </c>
       <c r="F103" s="45" t="n">
@@ -11966,7 +11955,7 @@
       </c>
       <c r="B104" s="44" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C104" s="45" t="inlineStr">
@@ -11976,12 +11965,12 @@
       </c>
       <c r="D104" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E104" s="44" t="inlineStr">
         <is>
-          <t>חימום 10 עוגות פרווה על הפלטה</t>
+          <t>עריכת שולחן: הכנת סלט כרוב וסלט טחינה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס), חצי מהמטבוחה, חצי מהחלות, צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F104" s="45" t="n">
@@ -11994,7 +11983,7 @@
       </c>
       <c r="B105" s="44" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C105" s="45" t="inlineStr">
@@ -12004,12 +11993,12 @@
       </c>
       <c r="D105" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E105" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F105" s="45" t="n">
@@ -12022,7 +12011,7 @@
       </c>
       <c r="B106" s="44" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C106" s="45" t="inlineStr">
@@ -12032,12 +12021,12 @@
       </c>
       <c r="D106" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E106" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F106" s="45" t="n">
@@ -12050,7 +12039,7 @@
       </c>
       <c r="B107" s="44" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C107" s="45" t="inlineStr">
@@ -12060,12 +12049,12 @@
       </c>
       <c r="D107" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E107" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הערב</t>
+          <t>הוצאת הגסטרונומים מתנור החימום</t>
         </is>
       </c>
       <c r="F107" s="45" t="n">
@@ -12078,7 +12067,7 @@
       </c>
       <c r="B108" s="44" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C108" s="45" t="inlineStr">
@@ -12088,12 +12077,12 @@
       </c>
       <c r="D108" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E108" s="44" t="inlineStr">
         <is>
-          <t>הורדת האוכל מהפלטות ומתנור החימום לארוחה</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F108" s="45" t="n">
@@ -12106,7 +12095,7 @@
       </c>
       <c r="B109" s="44" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="C109" s="45" t="inlineStr">
@@ -12116,12 +12105,12 @@
       </c>
       <c r="D109" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E109" s="44" t="inlineStr">
         <is>
-          <t>חיתוך אבטיח</t>
+          <t>הוצאת הגסטרונומים מתנור החימום</t>
         </is>
       </c>
       <c r="F109" s="45" t="n">
@@ -12134,7 +12123,7 @@
       </c>
       <c r="B110" s="44" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="C110" s="45" t="inlineStr">
@@ -12144,12 +12133,12 @@
       </c>
       <c r="D110" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E110" s="44" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
         </is>
       </c>
       <c r="F110" s="45" t="n">
@@ -12162,7 +12151,7 @@
       </c>
       <c r="B111" s="44" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C111" s="45" t="inlineStr">
@@ -12172,12 +12161,12 @@
       </c>
       <c r="D111" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E111" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>עריכת השולחן: הכנת סלט כרוב וסלט טחינה, והוצאת סלט חצילים, מטבוחה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס) וחלות</t>
         </is>
       </c>
       <c r="F111" s="45" t="n">
@@ -12190,7 +12179,7 @@
       </c>
       <c r="B112" s="44" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C112" s="45" t="inlineStr">
@@ -12200,12 +12189,12 @@
       </c>
       <c r="D112" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E112" s="44" t="inlineStr">
         <is>
-          <t>פריקת האוכל שמגיע מהקייטרינג</t>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
         </is>
       </c>
       <c r="F112" s="45" t="n">
@@ -12218,7 +12207,7 @@
       </c>
       <c r="B113" s="44" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C113" s="45" t="inlineStr">
@@ -12228,12 +12217,12 @@
       </c>
       <c r="D113" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E113" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל על הפלטות, וחיבור מיחמים בפינת קפה</t>
+          <t>הכנסת האוכל לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F113" s="45" t="n">
@@ -12246,7 +12235,7 @@
       </c>
       <c r="B114" s="44" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C114" s="45" t="inlineStr">
@@ -12256,12 +12245,12 @@
       </c>
       <c r="D114" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E114" s="44" t="inlineStr">
         <is>
-          <t>עריכת שולחן: טחינה, צלחות וסכו"ם, לחמניות, וסלטים מהקייטרינג אם יש</t>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם, וסידור שולחנות וכיסאות</t>
         </is>
       </c>
       <c r="F114" s="45" t="n">
@@ -12274,7 +12263,7 @@
       </c>
       <c r="B115" s="44" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C115" s="45" t="inlineStr">
@@ -12284,12 +12273,12 @@
       </c>
       <c r="D115" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E115" s="44" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: 10 עוגות פרווה, גרעינים, בקבוקים ואבטיח, כוסות ושתייה</t>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
         </is>
       </c>
       <c r="F115" s="45" t="n">
@@ -12302,7 +12291,7 @@
       </c>
       <c r="B116" s="44" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C116" s="45" t="inlineStr">
@@ -12312,12 +12301,12 @@
       </c>
       <c r="D116" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · ארוחת ערב וטיש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E116" s="44" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בסיום הטיש: טאטוא, שטיפת גסטרונומים וניקוי השולחנות</t>
+          <t>עריכת השולחן: הכנת סלט כרוב וסלט טחינה, והוצאת סלט חצילים, מטבוחה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס) וחלות</t>
         </is>
       </c>
       <c r="F116" s="45" t="n">
@@ -12330,7 +12319,7 @@
       </c>
       <c r="B117" s="44" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C117" s="45" t="inlineStr">
@@ -12340,12 +12329,12 @@
       </c>
       <c r="D117" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E117" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט טחינה — חצי כמות לארוחת הצהריים</t>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
         </is>
       </c>
       <c r="F117" s="45" t="n">
@@ -12358,7 +12347,7 @@
       </c>
       <c r="B118" s="44" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C118" s="45" t="inlineStr">
@@ -12368,12 +12357,12 @@
       </c>
       <c r="D118" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E118" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>הכנסת האוכל לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, אנטי פסטי, שווארמה טבעונית</t>
         </is>
       </c>
       <c r="F118" s="45" t="n">
@@ -12386,7 +12375,7 @@
       </c>
       <c r="B119" s="44" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C119" s="45" t="inlineStr">
@@ -12396,12 +12385,12 @@
       </c>
       <c r="D119" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E119" s="44" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם, וסידור שולחנות וכיסאות</t>
         </is>
       </c>
       <c r="F119" s="45" t="n">
@@ -12414,7 +12403,7 @@
       </c>
       <c r="B120" s="44" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C120" s="45" t="inlineStr">
@@ -12424,12 +12413,12 @@
       </c>
       <c r="D120" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E120" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
         </is>
       </c>
       <c r="F120" s="45" t="n">
@@ -12442,7 +12431,7 @@
       </c>
       <c r="B121" s="44" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C121" s="45" t="inlineStr">
@@ -12452,12 +12441,12 @@
       </c>
       <c r="D121" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E121" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>עריכת השולחן: הכנת סלט כרוב וסלט טחינה, והוצאת סלט חצילים, מטבוחה, סלטי קייטרינג (סלק אדום, ירקות מוחמצים, בטטה, כרוב במיונז, חומוס) וחלות</t>
         </is>
       </c>
       <c r="F121" s="45" t="n">
@@ -12470,7 +12459,7 @@
       </c>
       <c r="B122" s="44" t="inlineStr">
         <is>
-          <t>רוני פרנקל</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C122" s="45" t="inlineStr">
@@ -12480,12 +12469,12 @@
       </c>
       <c r="D122" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E122" s="44" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב — חצי כמות לארוחת הצהריים</t>
+          <t>פינוי השולחנות ושטיפת הגסטרונומים בסיום הארוחה</t>
         </is>
       </c>
       <c r="F122" s="45" t="n">
@@ -12498,7 +12487,7 @@
       </c>
       <c r="B123" s="44" t="inlineStr">
         <is>
-          <t>רוני פרנקל</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C123" s="45" t="inlineStr">
@@ -12508,12 +12497,12 @@
       </c>
       <c r="D123" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E123" s="44" t="inlineStr">
         <is>
-          <t>סידור שולחנות וכיסאות לארוחה, ופינוי הכל בסיום</t>
+          <t>חימום העוגות: 7 פסי עוגת דבש, 4 קראנצ'ים וחצי מהבראוניז — הכל פרווה</t>
         </is>
       </c>
       <c r="F123" s="45" t="n">
@@ -12526,7 +12515,7 @@
       </c>
       <c r="B124" s="44" t="inlineStr">
         <is>
-          <t>שירה אדלה לוזון</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C124" s="45" t="inlineStr">
@@ -12536,12 +12525,12 @@
       </c>
       <c r="D124" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E124" s="44" t="inlineStr">
         <is>
-          <t>הנחת האוכל בתנור החימום</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F124" s="45" t="n">
@@ -12554,7 +12543,7 @@
       </c>
       <c r="B125" s="44" t="inlineStr">
         <is>
-          <t>שירה אדלה לוזון</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C125" s="45" t="inlineStr">
@@ -12564,12 +12553,12 @@
       </c>
       <c r="D125" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · צהריים בשבת</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E125" s="44" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם</t>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
         </is>
       </c>
       <c r="F125" s="45" t="n">
@@ -12582,7 +12571,7 @@
       </c>
       <c r="B126" s="44" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C126" s="45" t="inlineStr">
@@ -12592,12 +12581,12 @@
       </c>
       <c r="D126" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E126" s="44" t="inlineStr">
         <is>
-          <t>חימום עוגות</t>
+          <t>פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
         </is>
       </c>
       <c r="F126" s="45" t="n">
@@ -12610,7 +12599,7 @@
       </c>
       <c r="B127" s="44" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C127" s="45" t="inlineStr">
@@ -12620,12 +12609,12 @@
       </c>
       <c r="D127" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E127" s="44" t="inlineStr">
         <is>
-          <t>הוצאת 15 עוגות, חלב, קורנפלקס, ענבים ואבטיח</t>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
         </is>
       </c>
       <c r="F127" s="45" t="n">
@@ -12648,12 +12637,12 @@
       </c>
       <c r="D128" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E128" s="44" t="inlineStr">
         <is>
-          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+          <t>חימום העוגות: 7 פסי עוגת דבש, 4 קראנצ'ים וחצי מהבראוניז — הכל פרווה</t>
         </is>
       </c>
       <c r="F128" s="45" t="n">
@@ -12666,7 +12655,7 @@
       </c>
       <c r="B129" s="44" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>מישל דוד</t>
         </is>
       </c>
       <c r="C129" s="45" t="inlineStr">
@@ -12676,12 +12665,12 @@
       </c>
       <c r="D129" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E129" s="44" t="inlineStr">
         <is>
-          <t>חיתוך האבטיח</t>
+          <t>פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
         </is>
       </c>
       <c r="F129" s="45" t="n">
@@ -12694,7 +12683,7 @@
       </c>
       <c r="B130" s="44" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>מישל דוד</t>
         </is>
       </c>
       <c r="C130" s="45" t="inlineStr">
@@ -12704,12 +12693,12 @@
       </c>
       <c r="D130" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש · קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E130" s="44" t="inlineStr">
         <is>
-          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
         </is>
       </c>
       <c r="F130" s="45" t="n">
@@ -12722,22 +12711,22 @@
       </c>
       <c r="B131" s="44" t="inlineStr">
         <is>
-          <t>אורי אסף</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C131" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D131" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E131" s="44" t="inlineStr">
         <is>
-          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+          <t>חיתוך 10 תפוחים</t>
         </is>
       </c>
       <c r="F131" s="45" t="n">
@@ -12750,22 +12739,22 @@
       </c>
       <c r="B132" s="44" t="inlineStr">
         <is>
-          <t>אורי אסף</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C132" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D132" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E132" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת החלות</t>
+          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
         </is>
       </c>
       <c r="F132" s="45" t="n">
@@ -12778,22 +12767,22 @@
       </c>
       <c r="B133" s="44" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C133" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D133" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E133" s="44" t="inlineStr">
         <is>
-          <t>תליית מחיצה</t>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
         </is>
       </c>
       <c r="F133" s="45" t="n">
@@ -12806,22 +12795,22 @@
       </c>
       <c r="B134" s="44" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>שירה אדלה לוזון</t>
         </is>
       </c>
       <c r="C134" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D134" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E134" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת עוגות השמרים</t>
+          <t>פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
         </is>
       </c>
       <c r="F134" s="45" t="n">
@@ -12834,22 +12823,22 @@
       </c>
       <c r="B135" s="44" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>שירה אדלה לוזון</t>
         </is>
       </c>
       <c r="C135" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D135" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E135" s="44" t="inlineStr">
         <is>
-          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
         </is>
       </c>
       <c r="F135" s="45" t="n">
@@ -12862,22 +12851,22 @@
       </c>
       <c r="B136" s="44" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C136" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D136" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E136" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת עוגות השמרים</t>
+          <t>הוצאת חלב, קורנפלקס וחצי מהענבים</t>
         </is>
       </c>
       <c r="F136" s="45" t="n">
@@ -12890,22 +12879,22 @@
       </c>
       <c r="B137" s="44" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C137" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D137" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E137" s="44" t="inlineStr">
         <is>
-          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+          <t>חימום העוגות</t>
         </is>
       </c>
       <c r="F137" s="45" t="n">
@@ -12918,22 +12907,22 @@
       </c>
       <c r="B138" s="44" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C138" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D138" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E138" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת החלות</t>
+          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
       </c>
       <c r="F138" s="45" t="n">
@@ -12946,22 +12935,22 @@
       </c>
       <c r="B139" s="44" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="C139" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D139" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E139" s="44" t="inlineStr">
         <is>
-          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+          <t>הוצאת העוגות: 4 פסי עוגת דבש, 3 קראנצ'ים, העוגיות וחצי מהבראוניז</t>
         </is>
       </c>
       <c r="F139" s="45" t="n">
@@ -12974,22 +12963,22 @@
       </c>
       <c r="B140" s="44" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>רוני פרנקל</t>
         </is>
       </c>
       <c r="C140" s="45" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D140" s="44" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E140" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת החלות</t>
+          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
         </is>
       </c>
       <c r="F140" s="45" t="n">
@@ -13002,7 +12991,7 @@
       </c>
       <c r="B141" s="44" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>אורי אסף</t>
         </is>
       </c>
       <c r="C141" s="45" t="inlineStr">
@@ -13017,7 +13006,7 @@
       </c>
       <c r="E141" s="44" t="inlineStr">
         <is>
-          <t>טאטוא ושטיפת רצפה</t>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
         </is>
       </c>
       <c r="F141" s="45" t="n">
@@ -13030,7 +13019,7 @@
       </c>
       <c r="B142" s="44" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>אורי אסף</t>
         </is>
       </c>
       <c r="C142" s="45" t="inlineStr">
@@ -13058,7 +13047,7 @@
       </c>
       <c r="B143" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי רוס</t>
         </is>
       </c>
       <c r="C143" s="45" t="inlineStr">
@@ -13086,7 +13075,7 @@
       </c>
       <c r="B144" s="44" t="inlineStr">
         <is>
-          <t>יהונתן קצב</t>
+          <t>איתי רוס</t>
         </is>
       </c>
       <c r="C144" s="45" t="inlineStr">
@@ -13114,7 +13103,7 @@
       </c>
       <c r="B145" s="44" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C145" s="45" t="inlineStr">
@@ -13129,7 +13118,7 @@
       </c>
       <c r="E145" s="44" t="inlineStr">
         <is>
-          <t>הנחת סידורים על הכסאות</t>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
         </is>
       </c>
       <c r="F145" s="45" t="n">
@@ -13142,7 +13131,7 @@
       </c>
       <c r="B146" s="44" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C146" s="45" t="inlineStr">
@@ -13170,7 +13159,7 @@
       </c>
       <c r="B147" s="44" t="inlineStr">
         <is>
-          <t>עומר יוסף גנון</t>
+          <t>אנה עזריאל</t>
         </is>
       </c>
       <c r="C147" s="45" t="inlineStr">
@@ -13185,7 +13174,7 @@
       </c>
       <c r="E147" s="44" t="inlineStr">
         <is>
-          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
         </is>
       </c>
       <c r="F147" s="45" t="n">
@@ -13198,7 +13187,7 @@
       </c>
       <c r="B148" s="44" t="inlineStr">
         <is>
-          <t>עומר יוסף גנון</t>
+          <t>אנה עזריאל</t>
         </is>
       </c>
       <c r="C148" s="45" t="inlineStr">
@@ -13213,7 +13202,7 @@
       </c>
       <c r="E148" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת עוגות השמרים</t>
+          <t>עזרה בהכנת החלות</t>
         </is>
       </c>
       <c r="F148" s="45" t="n">
@@ -13226,7 +13215,7 @@
       </c>
       <c r="B149" s="44" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C149" s="45" t="inlineStr">
@@ -13254,7 +13243,7 @@
       </c>
       <c r="B150" s="44" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C150" s="45" t="inlineStr">
@@ -13282,7 +13271,7 @@
       </c>
       <c r="B151" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C151" s="45" t="inlineStr">
@@ -13297,7 +13286,7 @@
       </c>
       <c r="E151" s="44" t="inlineStr">
         <is>
-          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+          <t>טאטוא ושטיפת רצפה</t>
         </is>
       </c>
       <c r="F151" s="45" t="n">
@@ -13310,7 +13299,7 @@
       </c>
       <c r="B152" s="44" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C152" s="45" t="inlineStr">
@@ -13338,7 +13327,7 @@
       </c>
       <c r="B153" s="44" t="inlineStr">
         <is>
-          <t>פנחס אליהו גלוסקין</t>
+          <t>יהונתן קצב</t>
         </is>
       </c>
       <c r="C153" s="45" t="inlineStr">
@@ -13353,7 +13342,7 @@
       </c>
       <c r="E153" s="44" t="inlineStr">
         <is>
-          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+          <t>תליית מחיצה</t>
         </is>
       </c>
       <c r="F153" s="45" t="n">
@@ -13366,7 +13355,7 @@
       </c>
       <c r="B154" s="44" t="inlineStr">
         <is>
-          <t>פנחס אליהו גלוסקין</t>
+          <t>יהונתן קצב</t>
         </is>
       </c>
       <c r="C154" s="45" t="inlineStr">
@@ -13394,7 +13383,7 @@
       </c>
       <c r="B155" s="44" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="C155" s="45" t="inlineStr">
@@ -13409,7 +13398,7 @@
       </c>
       <c r="E155" s="44" t="inlineStr">
         <is>
-          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+          <t>הנחת סידורים על הכסאות</t>
         </is>
       </c>
       <c r="F155" s="45" t="n">
@@ -13422,7 +13411,7 @@
       </c>
       <c r="B156" s="44" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="C156" s="45" t="inlineStr">
@@ -13450,7 +13439,7 @@
       </c>
       <c r="B157" s="44" t="inlineStr">
         <is>
-          <t>שליו שישו</t>
+          <t>עומר יוסף גנון</t>
         </is>
       </c>
       <c r="C157" s="45" t="inlineStr">
@@ -13465,7 +13454,7 @@
       </c>
       <c r="E157" s="44" t="inlineStr">
         <is>
-          <t>טאטוא ושטיפת רצפה</t>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
         </is>
       </c>
       <c r="F157" s="45" t="n">
@@ -13478,7 +13467,7 @@
       </c>
       <c r="B158" s="44" t="inlineStr">
         <is>
-          <t>שליו שישו</t>
+          <t>עומר יוסף גנון</t>
         </is>
       </c>
       <c r="C158" s="45" t="inlineStr">
@@ -13493,7 +13482,7 @@
       </c>
       <c r="E158" s="44" t="inlineStr">
         <is>
-          <t>עזרה בהכנת החלות</t>
+          <t>עזרה בהכנת עוגות השמרים</t>
         </is>
       </c>
       <c r="F158" s="45" t="n">
@@ -13506,7 +13495,7 @@
       </c>
       <c r="B159" s="44" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>עופר בביוף</t>
         </is>
       </c>
       <c r="C159" s="45" t="inlineStr">
@@ -13534,7 +13523,7 @@
       </c>
       <c r="B160" s="44" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>עופר בביוף</t>
         </is>
       </c>
       <c r="C160" s="45" t="inlineStr">
@@ -13562,7 +13551,7 @@
       </c>
       <c r="B161" s="44" t="inlineStr">
         <is>
-          <t>תמר פרידמן</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C161" s="45" t="inlineStr">
@@ -13577,7 +13566,7 @@
       </c>
       <c r="E161" s="44" t="inlineStr">
         <is>
-          <t>טאטוא ושטיפת רצפה</t>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
         </is>
       </c>
       <c r="F161" s="45" t="n">
@@ -13590,25 +13579,305 @@
       </c>
       <c r="B162" s="44" t="inlineStr">
         <is>
+          <t>עמית שי אברהם</t>
+        </is>
+      </c>
+      <c r="C162" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D162" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E162" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F162" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B163" s="44" t="inlineStr">
+        <is>
+          <t>פנחס אליהו גלוסקין</t>
+        </is>
+      </c>
+      <c r="C163" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D163" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E163" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F163" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B164" s="44" t="inlineStr">
+        <is>
+          <t>פנחס אליהו גלוסקין</t>
+        </is>
+      </c>
+      <c r="C164" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D164" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E164" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F164" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B165" s="44" t="inlineStr">
+        <is>
+          <t>שירה ספונוב</t>
+        </is>
+      </c>
+      <c r="C165" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D165" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E165" s="44" t="inlineStr">
+        <is>
+          <t>סידור כסאות בשורות — כולל 3 שורות עזרת ישראל</t>
+        </is>
+      </c>
+      <c r="F165" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B166" s="44" t="inlineStr">
+        <is>
+          <t>שירה ספונוב</t>
+        </is>
+      </c>
+      <c r="C166" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D166" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E166" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת עוגות השמרים</t>
+        </is>
+      </c>
+      <c r="F166" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B167" s="44" t="inlineStr">
+        <is>
+          <t>שליו שישו</t>
+        </is>
+      </c>
+      <c r="C167" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D167" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E167" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת רצפה</t>
+        </is>
+      </c>
+      <c r="F167" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B168" s="44" t="inlineStr">
+        <is>
+          <t>שליו שישו</t>
+        </is>
+      </c>
+      <c r="C168" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D168" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E168" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F168" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B169" s="44" t="inlineStr">
+        <is>
+          <t>של״ו רובינשטיין</t>
+        </is>
+      </c>
+      <c r="C169" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D169" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E169" s="44" t="inlineStr">
+        <is>
+          <t>העברת שולחנות לכיתת בית המדרש — לא בגרירה</t>
+        </is>
+      </c>
+      <c r="F169" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B170" s="44" t="inlineStr">
+        <is>
+          <t>של״ו רובינשטיין</t>
+        </is>
+      </c>
+      <c r="C170" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D170" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E170" s="44" t="inlineStr">
+        <is>
+          <t>עזרה בהכנת החלות</t>
+        </is>
+      </c>
+      <c r="F170" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B171" s="44" t="inlineStr">
+        <is>
           <t>תמר פרידמן</t>
         </is>
       </c>
-      <c r="C162" s="45" t="inlineStr">
+      <c r="C171" s="45" t="inlineStr">
         <is>
           <t>תורנות שישי</t>
         </is>
       </c>
-      <c r="D162" s="44" t="inlineStr">
+      <c r="D171" s="44" t="inlineStr">
         <is>
           <t>בית מדרש</t>
         </is>
       </c>
-      <c r="E162" s="44" t="inlineStr">
+      <c r="E171" s="44" t="inlineStr">
+        <is>
+          <t>טאטוא ושטיפת רצפה</t>
+        </is>
+      </c>
+      <c r="F171" s="45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="43" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B172" s="44" t="inlineStr">
+        <is>
+          <t>תמר פרידמן</t>
+        </is>
+      </c>
+      <c r="C172" s="45" t="inlineStr">
+        <is>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="D172" s="44" t="inlineStr">
+        <is>
+          <t>בית מדרש</t>
+        </is>
+      </c>
+      <c r="E172" s="44" t="inlineStr">
         <is>
           <t>עזרה בהכנת עוגות השמרים</t>
         </is>
       </c>
-      <c r="F162" s="45" t="n">
+      <c r="F172" s="45" t="n">
         <v>1</v>
       </c>
     </row>

--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -24,10 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -2676,7 +2675,11 @@
           <t>איתן וינסטון, זואי כהן, שירה ספונוב, אורי אסף, יונתן לירז</t>
         </is>
       </c>
-      <c r="H23" s="19" t="n"/>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
+        </is>
+      </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
           <t>סעודת שבת</t>
@@ -3192,7 +3195,11 @@
           <t>נדב טוקר, נגה שוהם, עפרי גזיאל</t>
         </is>
       </c>
-      <c r="H36" s="19" t="n"/>
+      <c r="H36" s="19" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
+        </is>
+      </c>
       <c r="I36" s="19" t="inlineStr">
         <is>
           <t>ארוחת צהריים</t>
@@ -5062,7 +5069,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="25" t="n"/>
     </row>
@@ -9187,7 +9193,6 @@
       </c>
       <c r="I132" s="33" t="n"/>
     </row>
-    <row r="133"/>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="25" t="inlineStr">
         <is>
@@ -9217,7 +9222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>

--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
@@ -1364,7 +1364,11 @@
           <t>קידוש</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n"/>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>חדר אוכל</t>
+        </is>
+      </c>
       <c r="E15" s="20" t="n"/>
       <c r="F15" s="21" t="n">
         <v>0.4583333333333333</v>
@@ -1437,7 +1441,7 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>שיעור</t>
+          <t>שיעור של שלמה</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
@@ -1445,11 +1449,7 @@
           <t>בית המדרש</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>של שלמה</t>
-        </is>
-      </c>
+      <c r="E18" s="20" t="n"/>
       <c r="F18" s="21" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>בית המדרש</t>
+          <t>חדר אוכל</t>
         </is>
       </c>
       <c r="E21" s="20" t="n"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
-          <t>עוגות שמרים — 6–8 קראנצ'ים (קינמון ושוקולד)</t>
+          <t>עוגות שמרים — 6–8 עוגות (קינמון ושוקולד)</t>
         </is>
       </c>
       <c r="F4" s="28" t="n">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="G4" s="31" t="inlineStr">
         <is>
-          <t>איתן כהן, חיים שמאי, הילה עזרא, איתי רוס</t>
+          <t>איתן כהן, חיים שמאי, הילה עזרא, ירדן בן שחר</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
-          <t>עוגות שמרים (קראנץ' קינמון ושוקולד)</t>
+          <t>עוגות שמרים (קינמון ושוקולד)</t>
         </is>
       </c>
       <c r="I4" s="19" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="J4" s="20" t="inlineStr">
         <is>
-          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית · לסמן 3 קראנצ'ים «סעודה שלישית»</t>
+          <t>בסיום — לרשום «שנה ב'» על הנייר כסף / השקית · לסמן 3 עוגות שמרים «סעודה שלישית»</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, ירדן בן שחר</t>
+          <t>הילה לביא, משה אוברשטיין</t>
         </is>
       </c>
       <c r="H6" s="19" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, יהב לוי</t>
+          <t>הילי אלפסי, יהב לוי</t>
         </is>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם, הלל פינגולד</t>
+          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
         </is>
       </c>
       <c r="H14" s="19" t="n"/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם, הלל פינגולד</t>
+          <t>אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
         </is>
       </c>
       <c r="H16" s="19" t="n"/>
@@ -2693,7 +2693,7 @@
       <c r="H22" s="19" t="n"/>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J22" s="20" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>חימום העוגות: 5 פסי עוגת דבש, 2 קראנצ'ים וחצי מהבראוניז — הכל פרווה</t>
+          <t>חימום העוגות: 5 פסי עוגת דבש, 2 עוגות שמרים וחצי מהבראוניז — הכל פרווה</t>
         </is>
       </c>
       <c r="F23" s="28" t="n">
@@ -2733,7 +2733,7 @@
       <c r="H23" s="19" t="n"/>
       <c r="I23" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J23" s="20" t="n"/>
@@ -2773,7 +2773,7 @@
       <c r="H24" s="19" t="n"/>
       <c r="I24" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J24" s="20" t="n"/>
@@ -2813,7 +2813,7 @@
       <c r="H25" s="19" t="n"/>
       <c r="I25" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J25" s="20" t="n"/>
@@ -2853,7 +2853,7 @@
       <c r="H26" s="19" t="n"/>
       <c r="I26" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J26" s="20" t="n"/>
@@ -2889,7 +2889,7 @@
       <c r="H27" s="19" t="n"/>
       <c r="I27" s="19" t="inlineStr">
         <is>
-          <t>טיש בחדר אוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J27" s="20" t="n"/>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>הוצאת העוגות: 3 פסי עוגת דבש, 2 קראנצ'ים, העוגיות וחצי מהבראוניז</t>
+          <t>הוצאת העוגות: 3 פסי עוגת דבש, 2 עוגות שמרים, העוגיות וחצי מהבראוניז</t>
         </is>
       </c>
       <c r="F31" s="28" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>הוצאת העוגות לסעודה שלישית: 3 פסי עוגת דבש ו-3 קראנצ'ים</t>
+          <t>הוצאת העוגות לסעודה שלישית: 3 פסי עוגת דבש ו-3 עוגות שמרים</t>
         </is>
       </c>
       <c r="F36" s="28" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="E4" s="31" t="inlineStr">
         <is>
-          <t>איתן כהן, חיים שמאי, הילה עזרא, איתי רוס</t>
+          <t>איתן כהן, חיים שמאי, הילה עזרא, ירדן בן שחר</t>
         </is>
       </c>
       <c r="F4" s="22">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, ירדן בן שחר</t>
+          <t>הילה לביא, משה אוברשטיין</t>
         </is>
       </c>
       <c r="F6" s="22">
@@ -4582,10 +4582,14 @@
       <c r="C7" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="35" t="n"/>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>הילי אלפסי</t>
+        </is>
+      </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, יהב לוי</t>
+          <t>הילי אלפסי, יהב לוי</t>
         </is>
       </c>
       <c r="F7" s="22">
@@ -4713,7 +4717,7 @@
       <c r="D11" s="35" t="n"/>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם, הלל פינגולד</t>
+          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
         </is>
       </c>
       <c r="F11" s="22">
@@ -5341,12 +5345,18 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E6" s="35" t="n"/>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>עוגיות שוקולד צ'יפס</t>
+        </is>
+      </c>
       <c r="F6" s="22">
         <f>IF(A6="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A6&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G6" s="36" t="n"/>
+      <c r="G6" s="36" t="n">
+        <v>3</v>
+      </c>
       <c r="H6" s="22">
         <f>IF(A6="","",SUMIF('היסטוריה'!$B$3:$B$3002,A6,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -5448,7 +5458,7 @@
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>עוגת דבש</t>
+          <t>עוגות שמרים</t>
         </is>
       </c>
       <c r="F9" s="22">
@@ -5705,7 +5715,7 @@
       </c>
       <c r="E16" s="35" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>עוגת דבש</t>
         </is>
       </c>
       <c r="F16" s="22">
@@ -6486,18 +6496,12 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
+      <c r="E37" s="35" t="n"/>
       <c r="F37" s="22">
         <f>IF(A37="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A37&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G37" s="36" t="n">
-        <v>3</v>
-      </c>
+      <c r="G37" s="36" t="n"/>
       <c r="H37" s="22">
         <f>IF(A37="","",SUMIF('היסטוריה'!$B$3:$B$3002,A37,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -7979,7 +7983,7 @@
       </c>
       <c r="E78" s="35" t="inlineStr">
         <is>
-          <t>עוגות שמרים</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F78" s="22">
@@ -10447,7 +10451,7 @@
       </c>
       <c r="B53" s="46" t="inlineStr">
         <is>
-          <t>איתי רוס</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C53" s="47" t="inlineStr">
@@ -10470,7 +10474,7 @@
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>הילה עזרא</t>
         </is>
       </c>
       <c r="C54" s="47" t="inlineStr">
@@ -10493,7 +10497,7 @@
       </c>
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>הילה עזרא</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C55" s="47" t="inlineStr">
@@ -10516,7 +10520,7 @@
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>חיים שמאי</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C56" s="47" t="inlineStr">
@@ -10539,7 +10543,7 @@
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C57" s="47" t="inlineStr">
@@ -10562,7 +10566,7 @@
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="C58" s="47" t="inlineStr">
@@ -10608,7 +10612,7 @@
       </c>
       <c r="B60" s="46" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C60" s="47" t="inlineStr">
@@ -11229,7 +11233,7 @@
       </c>
       <c r="B87" s="46" t="inlineStr">
         <is>
-          <t>איתן וינסטון</t>
+          <t>איתי רוס</t>
         </is>
       </c>
       <c r="C87" s="47" t="inlineStr">
@@ -11252,7 +11256,7 @@
       </c>
       <c r="B88" s="46" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C88" s="47" t="inlineStr">
@@ -11275,7 +11279,7 @@
       </c>
       <c r="B89" s="46" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C89" s="47" t="inlineStr">
@@ -11298,7 +11302,7 @@
       </c>
       <c r="B90" s="46" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C90" s="47" t="inlineStr">
@@ -11639,12 +11643,12 @@
       </c>
       <c r="B4" s="18" t="inlineStr">
         <is>
-          <t>עוגות שמרים (קראנץ' קינמון ושוקולד)</t>
+          <t>עוגות שמרים (קינמון ושוקולד)</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>6–8 קראנצ'ים</t>
+          <t>6–8 עוגות</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">

--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -1176,7 +1176,11 @@
         </is>
       </c>
       <c r="D8" s="19" t="n"/>
-      <c r="E8" s="20" t="n"/>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>הפרשת חלה 8:00</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="n">
         <v>0.3333333333333333</v>
       </c>
@@ -1328,7 +1332,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="E14" s="20" t="n"/>
       <c r="F14" s="21">
-        <f>IF($B$4="","",ROUND(($B$4+TIME(3,10,0))*288,0)/288)</f>
+        <f>IF($B$4="","",ROUND(($B$4+TIME(3,30,0))*288,0)/288)</f>
         <v/>
       </c>
       <c r="G14" s="22">
@@ -1838,7 +1842,7 @@
         </is>
       </c>
       <c r="C3" s="30" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
@@ -2359,7 +2363,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
+          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, איתי בן מנחם, איתי בן יהודה, עומר יוסף גנון, שירה אדלה לוזון, נועם ישראל קומפאס, פרת פולס, עשהאל ירושלמי, עופר בביוף, איתי רוס, תמר פרימור, אורי טילינגר, תמר פרידמן</t>
         </is>
       </c>
       <c r="H14" s="19" t="n"/>
@@ -2399,7 +2403,7 @@
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף</t>
+          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, איתי בן מנחם, איתי בן יהודה, עומר יוסף גנון, שירה אדלה לוזון</t>
         </is>
       </c>
       <c r="H15" s="19" t="n"/>
@@ -2439,7 +2443,7 @@
       </c>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
+          <t>נועם ישראל קומפאס, פרת פולס, עשהאל ירושלמי, עופר בביוף, איתי רוס, תמר פרימור, אורי טילינגר, תמר פרידמן</t>
         </is>
       </c>
       <c r="H16" s="19" t="n"/>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>אחיה נחמני, עומר יוסף גנון, מעיין רחל דינר</t>
+          <t>אחיה נחמני, רוני כהן, מעיין רחל דינר</t>
         </is>
       </c>
       <c r="H25" s="19" t="n"/>
@@ -2883,7 +2887,7 @@
       <c r="F27" s="28" t="n"/>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, מעיין יוספי, הדר עמדי, אחיה נחמני, עומר יוסף גנון</t>
+          <t>מעיין רחל דינר, מעיין יוספי, הדר עמדי, אחיה נחמני, רוני כהן</t>
         </is>
       </c>
       <c r="H27" s="19" t="n"/>
@@ -4717,7 +4721,7 @@
       <c r="D11" s="35" t="n"/>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, פרת פולס, עשהאל ירושלמי, נועם ישראל קומפאס, עופר בביוף, אלרואי גרינברג, איתי בן יהודה, תמר פרידמן, איתי רוס, אורי טילינגר, תמר פרימור, שירה אדלה לוזון, איתי בן מנחם</t>
+          <t>אלה מאיר, רותם דרור, איתן וינסטון, סהר שירון, איתי בן מנחם, איתי בן יהודה, עומר יוסף גנון, שירה אדלה לוזון, נועם ישראל קומפאס, פרת פולס, עשהאל ירושלמי, עופר בביוף, איתי רוס, תמר פרימור, אורי טילינגר, תמר פרידמן</t>
         </is>
       </c>
       <c r="F11" s="22">
@@ -4783,7 +4787,7 @@
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, מעיין יוספי, הדר עמדי, אחיה נחמני, עומר יוסף גנון</t>
+          <t>מעיין רחל דינר, מעיין יוספי, הדר עמדי, אחיה נחמני, רוני כהן</t>
         </is>
       </c>
       <c r="F13" s="22">
@@ -6262,18 +6266,12 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
+      <c r="E31" s="35" t="n"/>
       <c r="F31" s="22">
         <f>IF(A31="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A31&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G31" s="36" t="n">
-        <v>3</v>
-      </c>
+      <c r="G31" s="36" t="n"/>
       <c r="H31" s="22">
         <f>IF(A31="","",SUMIF('היסטוריה'!$B$3:$B$3002,A31,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -6381,7 +6379,7 @@
       </c>
       <c r="E34" s="35" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F34" s="22">
@@ -6389,7 +6387,7 @@
         <v/>
       </c>
       <c r="G34" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="22">
         <f>IF(A34="","",SUMIF('היסטוריה'!$B$3:$B$3002,A34,'היסטוריה'!$E$3:$E$3002))</f>
@@ -8547,12 +8545,18 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E94" s="35" t="n"/>
+      <c r="E94" s="35" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
       <c r="F94" s="22">
         <f>IF(A94="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A94&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G94" s="36" t="n"/>
+      <c r="G94" s="36" t="n">
+        <v>1</v>
+      </c>
       <c r="H94" s="22">
         <f>IF(A94="","",SUMIF('היסטוריה'!$B$3:$B$3002,A94,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -11026,7 +11030,7 @@
       </c>
       <c r="B78" s="46" t="inlineStr">
         <is>
-          <t>עומר יוסף גנון</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C78" s="47" t="inlineStr">
@@ -11302,7 +11306,7 @@
       </c>
       <c r="B90" s="46" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C90" s="47" t="inlineStr">
@@ -11325,7 +11329,7 @@
       </c>
       <c r="B91" s="46" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>סהר שירון</t>
         </is>
       </c>
       <c r="C91" s="47" t="inlineStr">
@@ -11348,7 +11352,7 @@
       </c>
       <c r="B92" s="46" t="inlineStr">
         <is>
-          <t>סהר שירון</t>
+          <t>עומר יוסף גנון</t>
         </is>
       </c>
       <c r="C92" s="47" t="inlineStr">

--- a/shabbatot/2026-09-18.xlsx
+++ b/shabbatot/2026-09-18.xlsx
@@ -12563,7 +12563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12602,86 +12602,198 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="19" t="n"/>
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת ערב</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>פרגית בגריל</t>
+        </is>
+      </c>
       <c r="C3" s="28" t="n"/>
       <c r="D3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n"/>
-      <c r="B4" s="19" t="n"/>
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת ערב</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>קוסקוס</t>
+        </is>
+      </c>
       <c r="C4" s="28" t="n"/>
       <c r="D4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n"/>
-      <c r="B5" s="19" t="n"/>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת ערב</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>לקט קוסקוס</t>
+        </is>
+      </c>
       <c r="C5" s="28" t="n"/>
       <c r="D5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n"/>
-      <c r="B6" s="19" t="n"/>
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת ערב</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>מוקפץ טבעוני</t>
+        </is>
+      </c>
       <c r="C6" s="28" t="n"/>
       <c r="D6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="19" t="n"/>
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>כתף בקר</t>
+        </is>
+      </c>
       <c r="C7" s="28" t="n"/>
       <c r="D7" s="20" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n"/>
-      <c r="B8" s="19" t="n"/>
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>אורז לבן</t>
+        </is>
+      </c>
       <c r="C8" s="28" t="n"/>
       <c r="D8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="19" t="n"/>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>תפו"א ובטטה</t>
+        </is>
+      </c>
       <c r="C9" s="28" t="n"/>
       <c r="D9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="n"/>
-      <c r="B10" s="19" t="n"/>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>אנטי פסטי</t>
+        </is>
+      </c>
       <c r="C10" s="28" t="n"/>
       <c r="D10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="19" t="n"/>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>שווארמה טבעונית</t>
+        </is>
+      </c>
       <c r="C11" s="28" t="n"/>
       <c r="D11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="19" t="n"/>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>סלק אדום</t>
+        </is>
+      </c>
       <c r="C12" s="28" t="n"/>
       <c r="D12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="19" t="n"/>
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>ירקות מוחמצים</t>
+        </is>
+      </c>
       <c r="C13" s="28" t="n"/>
       <c r="D13" s="20" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="19" t="n"/>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>בטטה</t>
+        </is>
+      </c>
       <c r="C14" s="28" t="n"/>
       <c r="D14" s="20" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="19" t="n"/>
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>כרוב במיונז</t>
+        </is>
+      </c>
       <c r="C15" s="28" t="n"/>
       <c r="D15" s="20" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="19" t="n"/>
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>סלטים</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>חומוס</t>
+        </is>
+      </c>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="20" t="n"/>
     </row>
@@ -12901,13 +13013,21 @@
       <c r="C52" s="28" t="n"/>
       <c r="D52" s="20" t="n"/>
     </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>המקור הוא data/catering.csv. משימה שכתוב בה {ארוחת ערב}, {ארוחת צהריים} או {סלטים} מקבלת את רשימת המנות של אותה ארוחה — כך התפריט מתעדכן בכל המשימות בבת אחת.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A54:D54"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="A3:A52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ארוחת ערב,קידוש,ארוחת צהריים,סעודה שלישית"</formula1>
+      <formula1>"ארוחת ערב,ארוחת צהריים,סלטים,קידוש,סעודה שלישית"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
